--- a/per-stock/AVGO/financials.xlsx
+++ b/per-stock/AVGO/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Cash flow (annual)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (quarterly)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Data flags" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,8 +24,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,6 +40,9 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <i val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -61,11 +70,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +544,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2013133668352</v>
+        <v>1957030658048</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +559,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2065016553472</v>
+        <v>2002309611520</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +574,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>82.721794</v>
+        <v>68.44426</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +589,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23.247448</v>
+        <v>21.220005</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +604,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29.482641</v>
+        <v>25.932959</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -606,7 +619,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.76725996</v>
+        <v>0.76284</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -621,7 +634,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.44943002</v>
+        <v>0.48988</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -636,7 +649,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.36571997</v>
+        <v>0.38848</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -651,7 +664,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.33370999</v>
+        <v>0.37280998</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -666,7 +679,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.295</v>
+        <v>0.479</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -681,7 +694,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14174000128</v>
+        <v>19627999232</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -696,7 +709,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>66056998912</v>
+        <v>64907001856</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -711,11 +724,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25503750144</v>
+        <v>32762000000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -726,7 +739,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4734668184</v>
+        <v>4757580198</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -741,7 +754,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>425.19</v>
+        <v>411.35</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -785,6 +798,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>AVGO — fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>2024-11-03</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Q2 FY26 (2026-05-03)</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>AVGO 10-K FY2025; 10-Q Q2 FY26 (filed 2026-06-09)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D50</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C50</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B50</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B46:E46)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue (annual sheet; TTM=Σ last 4 qtrs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D48</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C48</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B48</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B44:E44)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="5">
+        <f>B4/B3</f>
+        <v/>
+      </c>
+      <c r="C5" s="5">
+        <f>C4/C3</f>
+        <v/>
+      </c>
+      <c r="D5" s="5">
+        <f>D4/D3</f>
+        <v/>
+      </c>
+      <c r="E5" s="5">
+        <f>E4/E3</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = Gross profit / Revenue. Non-GAAP ~77% (excl. acq. intangible amort.) — see Data flags</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D40</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C40</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B40</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B36:E36)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income (yfinance line)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="5">
+        <f>B6/B3</f>
+        <v/>
+      </c>
+      <c r="C7" s="5">
+        <f>C6/C3</f>
+        <v/>
+      </c>
+      <c r="D7" s="5">
+        <f>D6/D3</f>
+        <v/>
+      </c>
+      <c r="E7" s="5">
+        <f>E6/E3</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> Operating income / Revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA (yfinance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex (statement-based)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="5">
+        <f>B9/B3</f>
+        <v/>
+      </c>
+      <c r="C10" s="5">
+        <f>C9/C3</f>
+        <v/>
+      </c>
+      <c r="D10" s="5">
+        <f>D9/D3</f>
+        <v/>
+      </c>
+      <c r="E10" s="5">
+        <f>E9/E3</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / Revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D7</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B7</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B7:E7)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capital Expenditure (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="5">
+        <f>B11/B3</f>
+        <v/>
+      </c>
+      <c r="C12" s="5">
+        <f>C11/C3</f>
+        <v/>
+      </c>
+      <c r="D12" s="5">
+        <f>D11/D3</f>
+        <v/>
+      </c>
+      <c r="E12" s="5">
+        <f>E11/E3</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> Capex / Revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D6</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C6</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B6</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B4</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Total debt − cash; TTM = MRQ (Q2 FY26)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="6">
+        <f>B13/B8</f>
+        <v/>
+      </c>
+      <c r="C14" s="6">
+        <f>C13/C8</f>
+        <v/>
+      </c>
+      <c r="D14" s="6">
+        <f>D13/D8</f>
+        <v/>
+      </c>
+      <c r="E14" s="6">
+        <f>E13/E8</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> Net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="7">
+        <f>'Balance sheet (annual)'!D4/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="7">
+        <f>'Balance sheet (annual)'!C4/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="7">
+        <f>'Balance sheet (annual)'!B4/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="7">
+        <f>'Balance sheet (quarterly)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5">
+        <f>C15/B15-1</f>
+        <v/>
+      </c>
+      <c r="D16" s="5">
+        <f>D15/C15-1</f>
+        <v/>
+      </c>
+      <c r="E16" s="5">
+        <f>E15/D15-1</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1834,13 +2318,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1850,6 +2334,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1860,30 +2345,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-10-31</t>
         </is>
@@ -1896,21 +2386,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-5747285.291214</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-10633068.944478</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>-34230000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>-40513718.070009</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>-2029498.525074</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>-36120000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1919,21 +2410,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.08094800000000001</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.103234</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.21</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.216651</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>0.023599</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>0.21</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1942,21 +2434,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>13142000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>11252000000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>10026000000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>8481000000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>8106000000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>8709000000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1965,21 +2458,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>-71000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>-103000000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>-163000000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>-187000000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>-86000000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>-172000000</v>
-      </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1988,21 +2482,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-71000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-103000000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>-163000000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>-187000000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>-86000000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>-172000000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2011,21 +2506,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>9310000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>7349000000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>8518000000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>4140000000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>4965000000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>5503000000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2034,21 +2530,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>2165000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>2153000000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>2233000000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>2202000000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>2166000000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>2174000000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2057,21 +2554,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>5113000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>4508000000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>4040000000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>3554000000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>3147000000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>3108000000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2080,21 +2578,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>13071000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>11149000000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>9863000000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>8294000000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>8020000000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>8537000000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2103,21 +2602,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>10906000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>8996000000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>7630000000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>6092000000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>5854000000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>6363000000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2126,21 +2626,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-776000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-801000000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-414000000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-807000000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-769000000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-873000000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2149,21 +2650,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>776000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>801000000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>761000000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>807000000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>769000000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>873000000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2172,21 +2674,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>9375252714.708786</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>7441366931.055522</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>8646770000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>4286486281.929991</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>5048970501.474926</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>5638880000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2195,21 +2698,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>9310000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>7349000000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>8518000000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>4140000000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>4965000000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>5503000000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2218,21 +2722,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>11328000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>10645000000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>10361000000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>9878000000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>9089000000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>8484000000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2241,21 +2746,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>10788000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>8563000000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>7508000000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>5887000000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>5829000000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>6260000000</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2264,21 +2770,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>4876000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>4888000000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>4889000000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>4860000000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>4826000000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>4836000000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2287,21 +2794,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>4747000000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>4741000000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>4732000000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>4714000000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>4707000000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>4695000000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2310,21 +2818,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>1.74</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>0.85</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>1.14</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2333,21 +2842,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>1.55</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>0.88</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>1.17</v>
-      </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2356,21 +2866,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>9310000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>7349000000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>8518000000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>4140000000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>4965000000</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>5503000000</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2379,21 +2890,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>9310000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>7349000000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>8518000000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>4140000000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>4965000000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>5503000000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2402,21 +2914,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>9310000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>7349000000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>8518000000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>4140000000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>4965000000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>5503000000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2425,21 +2938,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>9310000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>7349000000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>8518000000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>4140000000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>4965000000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>5503000000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2448,9 +2962,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="n">
         <v>0</v>
       </c>
@@ -2461,6 +2973,9 @@
         <v>0</v>
       </c>
       <c r="G26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3" t="n">
         <v>119000000</v>
       </c>
     </row>
@@ -2471,21 +2986,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>9310000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>7349000000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>8518000000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>4140000000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>4965000000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>5503000000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2494,21 +3010,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>820000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>846000000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>-1649000000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>1145000000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>120000000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>-13000000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2517,21 +3034,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>10130000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>8195000000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>6869000000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>5285000000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>5085000000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>5490000000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2540,21 +3058,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>47000000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>330000000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>-371000000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>18000000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>-61000000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>-69000000</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2563,21 +3082,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>118000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>433000000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>-208000000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>205000000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>25000000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>103000000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2586,21 +3106,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>-71000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>-103000000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>-146000000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>-187000000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>-86000000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>-172000000</v>
-      </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2609,21 +3130,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>71000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>103000000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>146000000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>187000000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>86000000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>172000000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2632,21 +3154,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>-776000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>-801000000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>-414000000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>-807000000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>-769000000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>-873000000</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2655,21 +3178,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>776000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>801000000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>761000000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>807000000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>769000000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>873000000</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2678,21 +3202,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>10859000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>8666000000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>7654000000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>6074000000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>5915000000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>6432000000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2701,21 +3226,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>4556000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>4491000000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>4595000000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>4629000000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>4282000000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>3713000000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2724,7 +3250,7 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>507000000</v>
+        <v>506000000</v>
       </c>
       <c r="C38" s="3" t="n">
         <v>507000000</v>
@@ -2733,12 +3259,13 @@
         <v>507000000</v>
       </c>
       <c r="E38" s="3" t="n">
+        <v>507000000</v>
+      </c>
+      <c r="F38" s="3" t="n">
         <v>506000000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>511000000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2747,7 +3274,7 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>507000000</v>
+        <v>506000000</v>
       </c>
       <c r="C39" s="3" t="n">
         <v>507000000</v>
@@ -2756,12 +3283,13 @@
         <v>507000000</v>
       </c>
       <c r="E39" s="3" t="n">
+        <v>507000000</v>
+      </c>
+      <c r="F39" s="3" t="n">
         <v>506000000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>511000000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2770,7 +3298,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>507000000</v>
+        <v>506000000</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>507000000</v>
@@ -2779,12 +3307,13 @@
         <v>507000000</v>
       </c>
       <c r="E40" s="3" t="n">
+        <v>507000000</v>
+      </c>
+      <c r="F40" s="3" t="n">
         <v>506000000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>511000000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2793,7 +3322,7 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>507000000</v>
+        <v>506000000</v>
       </c>
       <c r="C41" s="3" t="n">
         <v>507000000</v>
@@ -2802,12 +3331,13 @@
         <v>507000000</v>
       </c>
       <c r="E41" s="3" t="n">
+        <v>507000000</v>
+      </c>
+      <c r="F41" s="3" t="n">
         <v>506000000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>511000000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2816,21 +3346,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>2995000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>2965000000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>2981000000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>3050000000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>2693000000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>2253000000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2839,21 +3370,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>1055000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>1019000000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>1107000000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>1072000000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>1083000000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>949000000</v>
-      </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2862,21 +3394,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>15415000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>13157000000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>12249000000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>10703000000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>10197000000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>10145000000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2885,21 +3418,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>6772000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>6154000000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>5766000000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>5249000000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>4807000000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>4771000000</v>
-      </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2908,21 +3442,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>22187000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>19311000000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>18015000000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>15952000000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>15004000000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>14916000000</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2931,28 +3466,29 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>22187000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>19311000000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>18015000000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>15952000000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>15004000000</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>14916000000</v>
-      </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4425,13 +4961,19 @@
           <t>Allowance For Doubtful Accounts Receivable</t>
         </is>
       </c>
-      <c r="B74" s="3" t="n"/>
-      <c r="C74" s="3" t="n"/>
-      <c r="D74" s="3" t="n"/>
-      <c r="E74" s="3" t="n"/>
-      <c r="F74" s="3" t="n">
-        <v>-2597000000</v>
-      </c>
+      <c r="B74" s="3" t="n">
+        <v>-74000000</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>-101000000</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>-137000000</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>-126000000</v>
+      </c>
+      <c r="F74" s="3" t="n"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4439,13 +4981,19 @@
           <t>Gross Accounts Receivable</t>
         </is>
       </c>
-      <c r="B75" s="3" t="n"/>
-      <c r="C75" s="3" t="n"/>
-      <c r="D75" s="3" t="n"/>
-      <c r="E75" s="3" t="n"/>
-      <c r="F75" s="3" t="n">
-        <v>4668000000</v>
-      </c>
+      <c r="B75" s="3" t="n">
+        <v>7219000000</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>4517000000</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>3291000000</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>3084000000</v>
+      </c>
+      <c r="F75" s="3" t="n"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4492,13 +5040,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4844,21 +5392,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Net Preferred Stock Issuance</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>Common Stock Dividend Paid</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-11142000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-9814000000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-7645000000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-7032000000</v>
+      </c>
+      <c r="F17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Preferred Stock Issuance</t>
+          <t>Net Preferred Stock Issuance</t>
         </is>
       </c>
       <c r="B18" s="3" t="n"/>
@@ -4872,87 +5426,81 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Net Common Stock Issuance</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>-6089000000</v>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>-12202000000</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>-7563000000</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>-8341000000</v>
-      </c>
-      <c r="F19" s="3" t="n"/>
+          <t>Preferred Stock Issuance</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Common Stock Payments</t>
+          <t>Net Common Stock Issuance</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-6310000000</v>
+        <v>-6089000000</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-12392000000</v>
+        <v>-12202000000</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-7685000000</v>
+        <v>-7563000000</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-8455000000</v>
+        <v>-8341000000</v>
       </c>
       <c r="F20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Common Stock Issuance</t>
+          <t>Common Stock Payments</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>221000000</v>
+        <v>-6310000000</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>190000000</v>
+        <v>-12392000000</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>122000000</v>
+        <v>-7685000000</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>114000000</v>
+        <v>-8455000000</v>
       </c>
       <c r="F21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Net Issuance Payments Of Debt</t>
+          <t>Common Stock Issuance</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-2812000000</v>
+        <v>221000000</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>20346000000</v>
+        <v>190000000</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>-403000000</v>
+        <v>122000000</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>-426000000</v>
+        <v>114000000</v>
       </c>
       <c r="F22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Net Long Term Debt Issuance</t>
+          <t>Net Issuance Payments Of Debt</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
@@ -4972,67 +5520,67 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Long Term Debt Payments</t>
+          <t>Net Long Term Debt Issuance</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>-18478000000</v>
+        <v>-2812000000</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>-19608000000</v>
+        <v>20346000000</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>-403000000</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>-2361000000</v>
+        <v>-426000000</v>
       </c>
       <c r="F24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Long Term Debt Issuance</t>
+          <t>Long Term Debt Payments</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>15666000000</v>
+        <v>-18478000000</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>39954000000</v>
+        <v>-19608000000</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0</v>
+        <v>-403000000</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>1935000000</v>
+        <v>-2361000000</v>
       </c>
       <c r="F25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Investing Cash Flow</t>
+          <t>Long Term Debt Issuance</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-580000000</v>
+        <v>15666000000</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-23070000000</v>
+        <v>39954000000</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-689000000</v>
+        <v>0</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-667000000</v>
+        <v>1935000000</v>
       </c>
       <c r="F26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cash Flow From Continuing Investing Activities</t>
+          <t>Investing Cash Flow</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
@@ -5052,221 +5600,221 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Net Other Investing Changes</t>
+          <t>Cash Flow From Continuing Investing Activities</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>92000000</v>
+        <v>-580000000</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>-10000000</v>
+        <v>-23070000000</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>-66000000</v>
+        <v>-689000000</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>3000000</v>
+        <v>-667000000</v>
       </c>
       <c r="F28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Net Investment Purchase And Sale</t>
+          <t>Net Other Investing Changes</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-349000000</v>
+        <v>92000000</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-19000000</v>
+        <v>-10000000</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-118000000</v>
+        <v>-66000000</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0</v>
+        <v>3000000</v>
       </c>
       <c r="F29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sale Of Investment</t>
+          <t>Net Investment Purchase And Sale</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>248000000</v>
+        <v>-349000000</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>156000000</v>
+        <v>-19000000</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>228000000</v>
+        <v>-118000000</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>200000000</v>
+        <v>0</v>
       </c>
       <c r="F30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Purchase Of Investment</t>
+          <t>Sale Of Investment</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-597000000</v>
+        <v>248000000</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-175000000</v>
+        <v>156000000</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-346000000</v>
+        <v>228000000</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-200000000</v>
+        <v>200000000</v>
       </c>
       <c r="F31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Net Business Purchase And Sale</t>
+          <t>Purchase Of Investment</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>300000000</v>
+        <v>-597000000</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>-22493000000</v>
+        <v>-175000000</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>-53000000</v>
+        <v>-346000000</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>-246000000</v>
+        <v>-200000000</v>
       </c>
       <c r="F32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sale Of Business</t>
+          <t>Net Business Purchase And Sale</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
         <v>300000000</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>3485000000</v>
+        <v>-22493000000</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>0</v>
+        <v>-53000000</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>0</v>
+        <v>-246000000</v>
       </c>
       <c r="F33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Purchase Of Business</t>
+          <t>Sale Of Business</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>300000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>3485000000</v>
+      </c>
+      <c r="D34" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C34" s="3" t="n">
-        <v>-25978000000</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>-53000000</v>
-      </c>
       <c r="E34" s="3" t="n">
-        <v>-246000000</v>
+        <v>0</v>
       </c>
       <c r="F34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Net PPE Purchase And Sale</t>
+          <t>Purchase Of Business</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>-623000000</v>
+        <v>0</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-548000000</v>
+        <v>-25978000000</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-452000000</v>
+        <v>-53000000</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-424000000</v>
+        <v>-246000000</v>
       </c>
       <c r="F35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sale Of PPE</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="n"/>
-      <c r="E36" s="3" t="n"/>
-      <c r="F36" s="3" t="n">
-        <v>4000000</v>
-      </c>
+          <t>Net PPE Purchase And Sale</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>-623000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>-548000000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>-452000000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>-424000000</v>
+      </c>
+      <c r="F36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Purchase Of PPE</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>-623000000</v>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>-548000000</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>-452000000</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>-424000000</v>
-      </c>
-      <c r="F37" s="3" t="n"/>
+          <t>Sale Of PPE</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n">
+        <v>4000000</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Operating Cash Flow</t>
+          <t>Purchase Of PPE</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>27537000000</v>
+        <v>-623000000</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>19962000000</v>
+        <v>-548000000</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>18085000000</v>
+        <v>-452000000</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>16736000000</v>
+        <v>-424000000</v>
       </c>
       <c r="F38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cash Flow From Continuing Operating Activities</t>
+          <t>Operating Cash Flow</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
@@ -5286,67 +5834,67 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Change In Working Capital</t>
+          <t>Cash Flow From Continuing Operating Activities</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>-8500000000</v>
+        <v>27537000000</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>-4637000000</v>
+        <v>19962000000</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>-1643000000</v>
+        <v>18085000000</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>-1654000000</v>
+        <v>16736000000</v>
       </c>
       <c r="F40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Change In Other Working Capital</t>
+          <t>Change In Working Capital</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>-5155000000</v>
+        <v>-8500000000</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>-7235000000</v>
+        <v>-4637000000</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>-1692000000</v>
+        <v>-1643000000</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>-78000000</v>
+        <v>-1654000000</v>
       </c>
       <c r="F41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Change In Payables And Accrued Expense</t>
+          <t>Change In Other Working Capital</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>-118000000</v>
+        <v>-5155000000</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>121000000</v>
+        <v>-7235000000</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>209000000</v>
+        <v>-1692000000</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>-79000000</v>
+        <v>-78000000</v>
       </c>
       <c r="F42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Change In Payable</t>
+          <t>Change In Payables And Accrued Expense</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
@@ -5366,7 +5914,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Change In Account Payable</t>
+          <t>Change In Payable</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
@@ -5386,47 +5934,47 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Change In Inventory</t>
+          <t>Change In Account Payable</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>-510000000</v>
+        <v>-118000000</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>150000000</v>
+        <v>121000000</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>27000000</v>
+        <v>209000000</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>-627000000</v>
+        <v>-79000000</v>
       </c>
       <c r="F45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Change In Receivables</t>
+          <t>Change In Inventory</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>-2717000000</v>
+        <v>-510000000</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>2327000000</v>
+        <v>150000000</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>-187000000</v>
+        <v>27000000</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>-870000000</v>
+        <v>-627000000</v>
       </c>
       <c r="F46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Changes In Account Receivables</t>
+          <t>Change In Receivables</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
@@ -5446,67 +5994,67 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Other Non Cash Items</t>
+          <t>Changes In Account Receivables</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>438000000</v>
+        <v>-2717000000</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>831000000</v>
+        <v>2327000000</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>141000000</v>
+        <v>-187000000</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>312000000</v>
+        <v>-870000000</v>
       </c>
       <c r="F48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Stock Based Compensation</t>
+          <t>Other Non Cash Items</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>7568000000</v>
+        <v>438000000</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>5741000000</v>
+        <v>831000000</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>2171000000</v>
+        <v>141000000</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>1533000000</v>
+        <v>312000000</v>
       </c>
       <c r="F49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Deferred Tax</t>
+          <t>Stock Based Compensation</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>-4008000000</v>
+        <v>7568000000</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>1965000000</v>
+        <v>5741000000</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>-501000000</v>
+        <v>2171000000</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>-34000000</v>
+        <v>1533000000</v>
       </c>
       <c r="F50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Deferred Income Tax</t>
+          <t>Deferred Tax</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
@@ -5526,27 +6074,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Depreciation Amortization Depletion</t>
+          <t>Deferred Income Tax</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>8775000000</v>
+        <v>-4008000000</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>10010000000</v>
+        <v>1965000000</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>3835000000</v>
+        <v>-501000000</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>4984000000</v>
+        <v>-34000000</v>
       </c>
       <c r="F52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Depreciation And Amortization</t>
+          <t>Depreciation Amortization Depletion</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
@@ -5566,27 +6114,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Amortization Cash Flow</t>
+          <t>Depreciation And Amortization</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>8201000000</v>
+        <v>8775000000</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>9417000000</v>
+        <v>10010000000</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>3333000000</v>
+        <v>3835000000</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>4455000000</v>
+        <v>4984000000</v>
       </c>
       <c r="F54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Amortization Of Intangibles</t>
+          <t>Amortization Cash Flow</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
@@ -5606,1392 +6154,82 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Amortization Of Intangibles</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>574000000</v>
+        <v>8201000000</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>593000000</v>
+        <v>9417000000</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>502000000</v>
+        <v>3333000000</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>529000000</v>
+        <v>4455000000</v>
       </c>
       <c r="F56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Operating Gains Losses</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>138000000</v>
+        <v>574000000</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>157000000</v>
-      </c>
-      <c r="D57" s="3" t="n"/>
+        <v>593000000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>502000000</v>
+      </c>
       <c r="E57" s="3" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>198000000</v>
-      </c>
+        <v>529000000</v>
+      </c>
+      <c r="F57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>Operating Gains Losses</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>138000000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>157000000</v>
+      </c>
+      <c r="D58" s="3" t="n"/>
+      <c r="E58" s="3" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>198000000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B58" s="3" t="n">
+      <c r="B59" s="3" t="n">
         <v>23126000000</v>
       </c>
-      <c r="C58" s="3" t="n">
+      <c r="C59" s="3" t="n">
         <v>5895000000</v>
       </c>
-      <c r="D58" s="3" t="n">
+      <c r="D59" s="3" t="n">
         <v>14082000000</v>
       </c>
-      <c r="E58" s="3" t="n">
+      <c r="E59" s="3" t="n">
         <v>11495000000</v>
       </c>
-      <c r="F58" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G57"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>2025-04-30</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>2025-01-31</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>2024-10-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Free Cash Flow</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>8010000000</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>7466000000</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>7024000000</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>6411000000</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>6013000000</v>
-      </c>
-      <c r="G2" s="3" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Repurchase Of Capital Stock</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>-7850000000</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>-58000000</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>-4216000000</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>-2036000000</v>
-      </c>
-      <c r="G3" s="3" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Repayment Of Debt</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>-3650000000</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>-3638000000</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>-6750000000</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>-8090000000</v>
-      </c>
-      <c r="G4" s="3" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Issuance Of Debt</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>4474000000</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>4483000000</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>3587000000</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>630000000</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>6966000000</v>
-      </c>
-      <c r="G5" s="3" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Issuance Of Capital Stock</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n">
-        <v>103000000</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n">
-        <v>126000000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Capital Expenditure</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>-250000000</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>-237000000</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>-142000000</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>-144000000</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>-100000000</v>
-      </c>
-      <c r="G7" s="3" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Interest Paid Supplemental Data</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>619000000</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>699000000</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>602000000</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>700000000</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>671000000</v>
-      </c>
-      <c r="G8" s="3" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Income Tax Paid Supplemental Data</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>782000000</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>755000000</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>822000000</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>608000000</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>404000000</v>
-      </c>
-      <c r="G9" s="3" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>End Cash Position</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>14174000000</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>16178000000</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>10718000000</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>9472000000</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>9307000000</v>
-      </c>
-      <c r="G10" s="3" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Beginning Cash Position</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>16178000000</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>10718000000</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>9472000000</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>9307000000</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>9348000000</v>
-      </c>
-      <c r="G11" s="3" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Changes In Cash</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>-2004000000</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>5460000000</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>1246000000</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>165000000</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>-41000000</v>
-      </c>
-      <c r="G12" s="3" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Financing Cash Flow</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>-10149000000</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>-1876000000</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>-6014000000</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>-6257000000</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>-5980000000</v>
-      </c>
-      <c r="G13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Cash Flow From Continuing Financing Activities</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>-10149000000</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>-1876000000</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>-6014000000</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>-6257000000</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>-5980000000</v>
-      </c>
-      <c r="G14" s="3" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Net Other Financing Charges</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>-37000000</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>-27000000</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>-7000000</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>-4000000</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>-46000000</v>
-      </c>
-      <c r="G15" s="3" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Cash Dividends Paid</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>-3086000000</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>-2797000000</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>-2786000000</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>-2785000000</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>-2774000000</v>
-      </c>
-      <c r="G16" s="3" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Net Common Stock Issuance</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>-7850000000</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>103000000</v>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>-58000000</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>-4098000000</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>-2036000000</v>
-      </c>
-      <c r="G17" s="3" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Common Stock Payments</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>-7850000000</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>-58000000</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>-4216000000</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>-2036000000</v>
-      </c>
-      <c r="G18" s="3" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Common Stock Issuance</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n">
-        <v>103000000</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n">
-        <v>126000000</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Net Issuance Payments Of Debt</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>824000000</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>845000000</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>-3163000000</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>630000000</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>-1124000000</v>
-      </c>
-      <c r="G20" s="3" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Net Short Term Debt Issuance</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n">
-        <v>-3373000000</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>-119000000</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>3980000000</v>
-      </c>
-      <c r="G21" s="3" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Short Term Debt Issuance</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n">
-        <v>-3373000000</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>-119000000</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>3980000000</v>
-      </c>
-      <c r="G22" s="3" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Net Long Term Debt Issuance</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>824000000</v>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>1333000000</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>210000000</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>749000000</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>-5104000000</v>
-      </c>
-      <c r="G23" s="3" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Long Term Debt Payments</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>-3650000000</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>-3638000000</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>-6750000000</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>-8090000000</v>
-      </c>
-      <c r="G24" s="3" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Long Term Debt Issuance</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>4474000000</v>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>4971000000</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>6960000000</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>749000000</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>2986000000</v>
-      </c>
-      <c r="G25" s="3" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Investing Cash Flow</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>-115000000</v>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>-367000000</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>94000000</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>-133000000</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>-174000000</v>
-      </c>
-      <c r="G26" s="3" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Cash Flow From Continuing Investing Activities</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>-115000000</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>-367000000</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>94000000</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>-133000000</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>-174000000</v>
-      </c>
-      <c r="G27" s="3" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Net Other Investing Changes</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>105000000</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>-16000000</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>-10000000</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>13000000</v>
-      </c>
-      <c r="G28" s="3" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Net Investment Purchase And Sale</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>130000000</v>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>-235000000</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>-48000000</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>21000000</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>-87000000</v>
-      </c>
-      <c r="G29" s="3" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Sale Of Investment</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>244000000</v>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>101000000</v>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>51000000</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>78000000</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>18000000</v>
-      </c>
-      <c r="G30" s="3" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Purchase Of Investment</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>-114000000</v>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>-336000000</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>-99000000</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>-57000000</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>-105000000</v>
-      </c>
-      <c r="G31" s="3" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Net Business Purchase And Sale</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>300000000</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Sale Of Business</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n"/>
-      <c r="G33" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Purchase Of Business</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Net PPE Purchase And Sale</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="n">
-        <v>-250000000</v>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>-237000000</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>-142000000</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>-144000000</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>-100000000</v>
-      </c>
-      <c r="G35" s="3" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Purchase Of PPE</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="n">
-        <v>-250000000</v>
-      </c>
-      <c r="C36" s="3" t="n">
-        <v>-237000000</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>-142000000</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>-144000000</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>-100000000</v>
-      </c>
-      <c r="G36" s="3" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Operating Cash Flow</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>8260000000</v>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>7703000000</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>7166000000</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>6555000000</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>6113000000</v>
-      </c>
-      <c r="G37" s="3" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Cash Flow From Continuing Operating Activities</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="n">
-        <v>8260000000</v>
-      </c>
-      <c r="C38" s="3" t="n">
-        <v>7703000000</v>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>7166000000</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>6555000000</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>6113000000</v>
-      </c>
-      <c r="G38" s="3" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Change In Working Capital</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="n">
-        <v>-3105000000</v>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>-2345000000</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>-1894000000</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>-1910000000</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>-2351000000</v>
-      </c>
-      <c r="G39" s="3" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Change In Other Working Capital</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="n">
-        <v>-1632000000</v>
-      </c>
-      <c r="C40" s="3" t="n">
-        <v>-1722000000</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>-930000000</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>-598000000</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>-1905000000</v>
-      </c>
-      <c r="G40" s="3" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Change In Payables And Accrued Expense</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>534000000</v>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>118000000</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>136000000</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>-613000000</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>241000000</v>
-      </c>
-      <c r="G41" s="3" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Change In Payable</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>534000000</v>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>118000000</v>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>136000000</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>-613000000</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>241000000</v>
-      </c>
-      <c r="G42" s="3" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Change In Account Payable</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>534000000</v>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>118000000</v>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>136000000</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>-613000000</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>241000000</v>
-      </c>
-      <c r="G43" s="3" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Change In Inventory</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="n">
-        <v>-692000000</v>
-      </c>
-      <c r="C44" s="3" t="n">
-        <v>-90000000</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>-163000000</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>-109000000</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>-148000000</v>
-      </c>
-      <c r="G44" s="3" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Change In Receivables</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="n">
-        <v>-1315000000</v>
-      </c>
-      <c r="C45" s="3" t="n">
-        <v>-651000000</v>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>-937000000</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>-590000000</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>-539000000</v>
-      </c>
-      <c r="G45" s="3" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Changes In Account Receivables</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="n">
-        <v>-1315000000</v>
-      </c>
-      <c r="C46" s="3" t="n">
-        <v>-651000000</v>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>-937000000</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>-590000000</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>-539000000</v>
-      </c>
-      <c r="G46" s="3" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Other Non Cash Items</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="n">
-        <v>87000000</v>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v>107000000</v>
-      </c>
-      <c r="D47" s="3" t="n">
-        <v>59000000</v>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>134000000</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>138000000</v>
-      </c>
-      <c r="G47" s="3" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Stock Based Compensation</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="n">
-        <v>2176000000</v>
-      </c>
-      <c r="C48" s="3" t="n">
-        <v>2195000000</v>
-      </c>
-      <c r="D48" s="3" t="n">
-        <v>2322000000</v>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>1771000000</v>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>1280000000</v>
-      </c>
-      <c r="G48" s="3" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Deferred Tax</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="n">
-        <v>-455000000</v>
-      </c>
-      <c r="C49" s="3" t="n">
-        <v>-3025000000</v>
-      </c>
-      <c r="D49" s="3" t="n">
-        <v>284000000</v>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>-571000000</v>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>-696000000</v>
-      </c>
-      <c r="G49" s="3" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Deferred Income Tax</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="n">
-        <v>-455000000</v>
-      </c>
-      <c r="C50" s="3" t="n">
-        <v>-3025000000</v>
-      </c>
-      <c r="D50" s="3" t="n">
-        <v>284000000</v>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>-571000000</v>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>-696000000</v>
-      </c>
-      <c r="G50" s="3" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Depreciation Amortization Depletion</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="n">
-        <v>2153000000</v>
-      </c>
-      <c r="C51" s="3" t="n">
-        <v>2233000000</v>
-      </c>
-      <c r="D51" s="3" t="n">
-        <v>2202000000</v>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>2166000000</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>2174000000</v>
-      </c>
-      <c r="G51" s="3" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Depreciation And Amortization</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="n">
-        <v>2153000000</v>
-      </c>
-      <c r="C52" s="3" t="n">
-        <v>2233000000</v>
-      </c>
-      <c r="D52" s="3" t="n">
-        <v>2202000000</v>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>2166000000</v>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>2174000000</v>
-      </c>
-      <c r="G52" s="3" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Amortization Cash Flow</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="n">
-        <v>2003000000</v>
-      </c>
-      <c r="C53" s="3" t="n">
-        <v>2085000000</v>
-      </c>
-      <c r="D53" s="3" t="n">
-        <v>2060000000</v>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>2024000000</v>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>2032000000</v>
-      </c>
-      <c r="G53" s="3" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Amortization Of Intangibles</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="n">
-        <v>2003000000</v>
-      </c>
-      <c r="C54" s="3" t="n">
-        <v>2085000000</v>
-      </c>
-      <c r="D54" s="3" t="n">
-        <v>2060000000</v>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>2024000000</v>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>2032000000</v>
-      </c>
-      <c r="G54" s="3" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="n">
-        <v>150000000</v>
-      </c>
-      <c r="C55" s="3" t="n">
-        <v>148000000</v>
-      </c>
-      <c r="D55" s="3" t="n">
-        <v>142000000</v>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>142000000</v>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>142000000</v>
-      </c>
-      <c r="G55" s="3" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Operating Gains Losses</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="n">
-        <v>55000000</v>
-      </c>
-      <c r="C56" s="3" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="D56" s="3" t="n">
-        <v>53000000</v>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="3" t="n">
-        <v>65000000</v>
-      </c>
-      <c r="G56" s="3" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Net Income From Continuing Operations</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="n">
-        <v>7349000000</v>
-      </c>
-      <c r="C57" s="3" t="n">
-        <v>8518000000</v>
-      </c>
-      <c r="D57" s="3" t="n">
-        <v>4140000000</v>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v>4965000000</v>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>5503000000</v>
-      </c>
-      <c r="G57" s="3" t="n"/>
+      <c r="F59" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7004,7 +6242,1427 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:H58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Free Cash Flow</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>10262000000</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>8010000000</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>7466000000</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>7024000000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>6411000000</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Repurchase Of Capital Stock</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>-600000000</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>-7850000000</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>-58000000</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>-4216000000</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Repayment Of Debt</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>-1250000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>-3650000000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>-3638000000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>-6750000000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Issuance Of Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>4474000000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>4483000000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>3587000000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>630000000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Issuance Of Capital Stock</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n">
+        <v>103000000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n">
+        <v>126000000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Capital Expenditure</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>-231000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>-250000000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>-237000000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>-142000000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>-144000000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Interest Paid Supplemental Data</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>695000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>619000000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>699000000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>602000000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>700000000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Income Tax Paid Supplemental Data</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>1099000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>782000000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>755000000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>822000000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>608000000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>End Cash Position</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>19628000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>14174000000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>16178000000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>10718000000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>9472000000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Beginning Cash Position</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>14174000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>16178000000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>10718000000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>9472000000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>9307000000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Changes In Cash</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>5454000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>-2004000000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>5460000000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>1246000000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>165000000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Financing Cash Flow</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>-4831000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-10149000000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>-1876000000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-6014000000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>-6257000000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cash Flow From Continuing Financing Activities</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>-4831000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>-10149000000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>-1876000000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>-6014000000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>-6257000000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Net Other Financing Charges</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>-2000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>-37000000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>-27000000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>-7000000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>-4000000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Cash Dividends Paid</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>-3092000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-3086000000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-2797000000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-2786000000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-2785000000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Common Stock Dividend Paid</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-3092000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-3086000000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-2797000000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-2786000000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-2785000000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Net Common Stock Issuance</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>-487000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>-7850000000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>103000000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>-58000000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>-4098000000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Common Stock Payments</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>-600000000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>-7850000000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>-58000000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>-4216000000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Common Stock Issuance</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n">
+        <v>103000000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n">
+        <v>126000000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Net Issuance Payments Of Debt</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>-1250000000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>824000000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>845000000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-3163000000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>630000000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Net Short Term Debt Issuance</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="n">
+        <v>-3373000000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>-119000000</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>3980000000</v>
+      </c>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Short Term Debt Issuance</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n">
+        <v>-3373000000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>-119000000</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>3980000000</v>
+      </c>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Net Long Term Debt Issuance</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>-1250000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>824000000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1333000000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>210000000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>749000000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Long Term Debt Payments</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>-1250000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>-3650000000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>-3638000000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-6750000000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Long Term Debt Issuance</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>4474000000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>4971000000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>6960000000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>749000000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Investing Cash Flow</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>-208000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-115000000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-367000000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>94000000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>-133000000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Cash Flow From Continuing Investing Activities</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>-208000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>-115000000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>-367000000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>94000000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>-133000000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Net Other Investing Changes</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>105000000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>-16000000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>-10000000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Net Investment Purchase And Sale</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>130000000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>-235000000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>-48000000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sale Of Investment</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>39000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>244000000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>101000000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>51000000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>78000000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Purchase Of Investment</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>-23000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>-114000000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>-336000000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>-99000000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>-57000000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Net Business Purchase And Sale</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>300000000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sale Of Business</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Purchase Of Business</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Net PPE Purchase And Sale</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>-231000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>-250000000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>-237000000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>-142000000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>-144000000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Purchase Of PPE</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>-231000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>-250000000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>-237000000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>-142000000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>-144000000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Operating Cash Flow</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>10493000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>8260000000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>7703000000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>7166000000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>6555000000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Cash Flow From Continuing Operating Activities</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>10493000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>8260000000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>7703000000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>7166000000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>6555000000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Change In Working Capital</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>-2572000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>-3105000000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>-2345000000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>-1894000000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>-1910000000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Change In Other Working Capital</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>1015000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>-1632000000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>-1722000000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>-930000000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>-598000000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Change In Payables And Accrued Expense</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>149000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>534000000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>118000000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>136000000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>-613000000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Change In Payable</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>149000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>534000000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>118000000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>136000000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>-613000000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Change In Account Payable</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>149000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>534000000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>118000000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>136000000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>-613000000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Change In Inventory</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>-1366000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>-692000000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>-90000000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>-163000000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>-109000000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Change In Receivables</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>-2370000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>-1315000000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>-651000000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>-937000000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>-590000000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Changes In Account Receivables</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>-2370000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>-1315000000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>-651000000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>-937000000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>-590000000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Other Non Cash Items</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>87000000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>107000000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>59000000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>134000000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Stock Based Compensation</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>2092000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>2176000000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>2195000000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>2322000000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>1771000000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Deferred Tax</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>-603000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>-455000000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>-3025000000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>284000000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>-571000000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Deferred Income Tax</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>-603000000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>-455000000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>-3025000000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>284000000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>-571000000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Depreciation Amortization Depletion</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>2165000000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>2153000000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>2233000000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>2202000000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>2166000000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Depreciation And Amortization</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>2165000000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>2153000000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>2233000000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>2202000000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>2166000000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Amortization Cash Flow</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>2002000000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>2003000000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>2085000000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>2060000000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>2024000000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Amortization Of Intangibles</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>2002000000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>2003000000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>2085000000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>2060000000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>2024000000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>163000000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>150000000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>148000000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>142000000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>142000000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Operating Gains Losses</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>31000000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>53000000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Net Income From Continuing Operations</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>9310000000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>7349000000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>8518000000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>4140000000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>4965000000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7026,14 +7684,1810 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Gross margin basis</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>no gaps detected</t>
-        </is>
-      </c>
+          <t>FY Summary uses GAAP gross margin (~68%). Non-GAAP ~77% (Q2 FY26 77.1%) excludes amortization of acquired (VMware) intangibles in COGS. Watchlist 'Gross Mgn %' 76.3% is the non-GAAP/info.grossMargins basis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Operating income line</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Uses yfinance 'Operating Income'; 'Total Operating Income As Reported' is ~$0.6B lower (FY25 25,484 vs 26,075) — item classification.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>4758000000</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>4736000000</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>4741000000</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>4722000000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>4703000000</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>4758000000</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>4736000000</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>4741000000</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>4722000000</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>4703000000</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>45279000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>51883000000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>48958000000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>53501000000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>57799000000</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>64907000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>66057000000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>65136000000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>64229000000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>67282000000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>-38443000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>-48231000000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>-48782000000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>-58868000000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>-64608000000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>152598000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>145929000000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>146428000000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>137496000000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>136857000000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>23351000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>15203000000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>13059000000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>8294000000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1584000000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>-38443000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>-48231000000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>-48782000000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-58868000000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>-64608000000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>39000000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>87691000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>79872000000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>81292000000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>73277000000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>69586000000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>150346000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>143677000000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>143276000000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>136100000000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>131330000000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>87691000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>79872000000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>81292000000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>73277000000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>69586000000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>87691000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>79872000000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>81292000000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>73277000000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>69586000000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>208000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>212000000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>218000000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>221000000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>206000000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>208000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>212000000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>218000000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>221000000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>206000000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>12166000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>6520000000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>9761000000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>4040000000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>2686000000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>75312000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>73135000000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>71308000000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>69011000000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>66689000000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>91467000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>90031000000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>89800000000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>92344000000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>95044000000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>72605000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>73172000000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>71286000000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>75640000000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>74447000000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>2469000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>1810000000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1423000000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>1410000000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>1445000000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Tradeand Other Payables Non Current</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>1662000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>1668000000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>1628000000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>3817000000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>3732000000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>5819000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>5889000000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>6251000000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>7583000000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>7519000000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>4204000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>3667000000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>3547000000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>4031000000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>4154000000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>1615000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>2222000000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>2704000000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>3552000000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>3365000000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>62655000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>63805000000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>61984000000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>62830000000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>61751000000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>13000000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>62655000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>63805000000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>61984000000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>62823000000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>61744000000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>18862000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>16859000000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>18514000000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>16704000000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>20597000000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>1228000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>682000000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>663000000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>795000000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>992000000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>10038000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>9188000000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>9469000000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>10305000000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>10303000000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>10038000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>9188000000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>9469000000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>10305000000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>10303000000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>2252000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>2252000000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>3152000000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>1399000000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>5531000000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>26000000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>2252000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>2252000000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>3152000000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>1396000000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>5527000000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>2252000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>2252000000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>3152000000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>900000000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>1650000000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Commercial Paper</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n"/>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="n">
+        <v>496000000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>3877000000</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>3992000000</v>
+      </c>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>1134000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>864000000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>2129000000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>1719000000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>1266000000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>4210000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>3873000000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>3101000000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>2486000000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>2505000000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>656000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>673000000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>620000000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>644000000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>562000000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Interest Payable</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>656000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>673000000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>620000000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>644000000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>562000000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>3554000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>3200000000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>2481000000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>1842000000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>1943000000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>1217000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>1088000000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>921000000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>410000000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>646000000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>2337000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>2112000000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>1560000000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>1432000000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>1297000000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>179158000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>169903000000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>171092000000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>165621000000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>164630000000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>136945000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>137841000000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>139519000000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>140623000000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>142449000000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>8023000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>7139000000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>6915000000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>6027000000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>5793000000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>126134000000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>128103000000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>130074000000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>132145000000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>134194000000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>28333000000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>30302000000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>32273000000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>34344000000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>36393000000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>97801000000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>97801000000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>97801000000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>97801000000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>97801000000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>2788000000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>2599000000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>2530000000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>2451000000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>2462000000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n"/>
+      <c r="C55" s="3" t="n"/>
+      <c r="D55" s="3" t="n">
+        <v>-4896000000</v>
+      </c>
+      <c r="E55" s="3" t="n"/>
+      <c r="F55" s="3" t="n"/>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n">
+        <v>-4504000000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n"/>
+      <c r="C56" s="3" t="n"/>
+      <c r="D56" s="3" t="n">
+        <v>7426000000</v>
+      </c>
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="3" t="n"/>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n">
+        <v>7025000000</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n"/>
+      <c r="C57" s="3" t="n"/>
+      <c r="D57" s="3" t="n">
+        <v>78000000</v>
+      </c>
+      <c r="E57" s="3" t="n"/>
+      <c r="F57" s="3" t="n"/>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n">
+        <v>57000000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n"/>
+      <c r="C58" s="3" t="n"/>
+      <c r="D58" s="3" t="n">
+        <v>5656000000</v>
+      </c>
+      <c r="E58" s="3" t="n"/>
+      <c r="F58" s="3" t="n"/>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n">
+        <v>5246000000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n"/>
+      <c r="C59" s="3" t="n"/>
+      <c r="D59" s="3" t="n">
+        <v>1488000000</v>
+      </c>
+      <c r="E59" s="3" t="n"/>
+      <c r="F59" s="3" t="n"/>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n">
+        <v>1518000000</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n"/>
+      <c r="C60" s="3" t="n"/>
+      <c r="D60" s="3" t="n">
+        <v>204000000</v>
+      </c>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n">
+        <v>204000000</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n"/>
+      <c r="C61" s="3" t="n"/>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3" t="n"/>
+      <c r="F61" s="3" t="n"/>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>42213000000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>32062000000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>31573000000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>24998000000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>22181000000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>369000000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>289000000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>457000000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>656000000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>959000000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>1140000000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>641000000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>518000000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>793000000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>936000000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>4328000000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>2962000000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>2270000000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>2180000000</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>2017000000</v>
+      </c>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Finished Goods</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>1858000000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>842000000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>682000000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>477000000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Work In Process</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>1801000000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>1544000000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>1280000000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>1349000000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>1119000000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Raw Materials</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>669000000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>576000000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>308000000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>354000000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>398000000</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>16748000000</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>13996000000</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>12150000000</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>10651000000</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>8797000000</v>
+      </c>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>5918000000</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>5536000000</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>5005000000</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>4157000000</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>3234000000</v>
+      </c>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>10830000000</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>8460000000</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>7145000000</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>6494000000</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>5563000000</v>
+      </c>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n"/>
+      <c r="C72" s="3" t="n"/>
+      <c r="D72" s="3" t="n">
+        <v>-74000000</v>
+      </c>
+      <c r="E72" s="3" t="n"/>
+      <c r="F72" s="3" t="n"/>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n">
+        <v>-101000000</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n"/>
+      <c r="C73" s="3" t="n"/>
+      <c r="D73" s="3" t="n">
+        <v>7219000000</v>
+      </c>
+      <c r="E73" s="3" t="n"/>
+      <c r="F73" s="3" t="n"/>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="3" t="n">
+        <v>4517000000</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>19628000000</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>14174000000</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>16178000000</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>10718000000</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>9472000000</v>
+      </c>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>19628000000</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>14174000000</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>16178000000</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>10718000000</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>9472000000</v>
+      </c>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/per-stock/AVGO/financials.xlsx
+++ b/per-stock/AVGO/financials.xlsx
@@ -12,10 +12,10 @@
     <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Cash flow (annual)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Cash flow (quarterly)" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Data flags" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Balance sheet (quarterly)" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,7 +29,7 @@
     <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,9 +40,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <i val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -70,12 +67,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -811,13 +807,13 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AVGO — fiscal-year summary (GAAP, $ except where noted)</t>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -847,34 +843,34 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Fiscal period end</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>2024-11-03</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Q2 FY26 (2026-05-03)</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>AVGO 10-K FY2025; 10-Q Q2 FY26 (filed 2026-06-09)</t>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-04-30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
         </is>
       </c>
     </row>
@@ -902,7 +898,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Total Revenue (annual sheet; TTM=Σ last 4 qtrs)</t>
+          <t>Total Revenue</t>
         </is>
       </c>
     </row>
@@ -940,25 +936,25 @@
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B5" s="5">
-        <f>B4/B3</f>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
         <v/>
       </c>
-      <c r="C5" s="5">
-        <f>C4/C3</f>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
         <v/>
       </c>
-      <c r="D5" s="5">
-        <f>D4/D3</f>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
         <v/>
       </c>
-      <c r="E5" s="5">
-        <f>E4/E3</f>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
         <v/>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GAAP = Gross profit / Revenue. Non-GAAP ~77% (excl. acq. intangible amort.) — see Data flags</t>
+          <t>GAAP = gross profit / revenue</t>
         </is>
       </c>
     </row>
@@ -986,7 +982,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Operating Income (yfinance line)</t>
+          <t>Operating Income</t>
         </is>
       </c>
     </row>
@@ -996,24 +992,24 @@
           <t>Operating margin %</t>
         </is>
       </c>
-      <c r="B7" s="5">
-        <f>B6/B3</f>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
         <v/>
       </c>
-      <c r="C7" s="5">
-        <f>C6/C3</f>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
         <v/>
       </c>
-      <c r="D7" s="5">
-        <f>D6/D3</f>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
         <v/>
       </c>
-      <c r="E7" s="5">
-        <f>E6/E3</f>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
         <v/>
       </c>
       <c r="F7">
-        <f> Operating income / Revenue</f>
+        <f> operating income / revenue</f>
         <v/>
       </c>
     </row>
@@ -1041,7 +1037,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>EBITDA (yfinance)</t>
+          <t>EBITDA</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1065,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FCF = OCF − capex (statement-based)</t>
+          <t>FCF = OCF − capex</t>
         </is>
       </c>
     </row>
@@ -1079,24 +1075,24 @@
           <t>FCF margin %</t>
         </is>
       </c>
-      <c r="B10" s="5">
-        <f>B9/B3</f>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
         <v/>
       </c>
-      <c r="C10" s="5">
-        <f>C9/C3</f>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
         <v/>
       </c>
-      <c r="D10" s="5">
-        <f>D9/D3</f>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
         <v/>
       </c>
-      <c r="E10" s="5">
-        <f>E9/E3</f>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
         <v/>
       </c>
       <c r="F10">
-        <f> FCF / Revenue</f>
+        <f> FCF / revenue</f>
         <v/>
       </c>
     </row>
@@ -1124,7 +1120,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Capital Expenditure (shown positive)</t>
+          <t>Capex (shown positive)</t>
         </is>
       </c>
     </row>
@@ -1134,24 +1130,24 @@
           <t>Capex / revenue %</t>
         </is>
       </c>
-      <c r="B12" s="5">
-        <f>B11/B3</f>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
         <v/>
       </c>
-      <c r="C12" s="5">
-        <f>C11/C3</f>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
         <v/>
       </c>
-      <c r="D12" s="5">
-        <f>D11/D3</f>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
         <v/>
       </c>
-      <c r="E12" s="5">
-        <f>E11/E3</f>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
         <v/>
       </c>
       <c r="F12">
-        <f> Capex / Revenue</f>
+        <f> capex / revenue</f>
         <v/>
       </c>
     </row>
@@ -1179,7 +1175,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Total debt − cash; TTM = MRQ (Q2 FY26)</t>
+          <t>Net debt; TTM = MRQ</t>
         </is>
       </c>
     </row>
@@ -1189,24 +1185,24 @@
           <t>Net debt / EBITDA</t>
         </is>
       </c>
-      <c r="B14" s="6">
-        <f>B13/B8</f>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
         <v/>
       </c>
-      <c r="C14" s="6">
-        <f>C13/C8</f>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
         <v/>
       </c>
-      <c r="D14" s="6">
-        <f>D13/D8</f>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
         <v/>
       </c>
-      <c r="E14" s="6">
-        <f>E13/E8</f>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
         <v/>
       </c>
       <c r="F14">
-        <f> Net debt / EBITDA</f>
+        <f> net debt / EBITDA</f>
         <v/>
       </c>
     </row>
@@ -1216,25 +1212,25 @@
           <t>Share count (period-end, M)</t>
         </is>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="6">
         <f>'Balance sheet (annual)'!D4/1e6</f>
         <v/>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="6">
         <f>'Balance sheet (annual)'!C4/1e6</f>
         <v/>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="6">
         <f>'Balance sheet (annual)'!B4/1e6</f>
         <v/>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="6">
         <f>'Balance sheet (quarterly)'!B2/1e6</f>
         <v/>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ordinary Shares Number ÷ 1e6; TTM = MRQ</t>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
         </is>
       </c>
     </row>
@@ -1244,17 +1240,17 @@
           <t>Share count YoY %</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="5">
-        <f>C15/B15-1</f>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
         <v/>
       </c>
-      <c r="D16" s="5">
-        <f>D15/C15-1</f>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
         <v/>
       </c>
-      <c r="E16" s="5">
-        <f>E15/D15-1</f>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
         <v/>
       </c>
       <c r="F16" t="inlineStr">
@@ -5046,6 +5042,1790 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>4758000000</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>4736000000</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>4741000000</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>4722000000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>4703000000</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>4758000000</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>4736000000</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>4741000000</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>4722000000</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>4703000000</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>45279000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>51883000000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>48958000000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>53501000000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>57799000000</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>64907000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>66057000000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>65136000000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>64229000000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>67282000000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>-38443000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>-48231000000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>-48782000000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>-58868000000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>-64608000000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>152598000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>145929000000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>146428000000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>137496000000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>136857000000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>23351000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>15203000000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>13059000000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>8294000000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1584000000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>-38443000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>-48231000000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>-48782000000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-58868000000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>-64608000000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>39000000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>87691000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>79872000000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>81292000000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>73277000000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>69586000000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>150346000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>143677000000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>143276000000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>136100000000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>131330000000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>87691000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>79872000000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>81292000000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>73277000000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>69586000000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>87691000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>79872000000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>81292000000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>73277000000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>69586000000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>208000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>212000000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>218000000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>221000000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>206000000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>208000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>212000000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>218000000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>221000000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>206000000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>12166000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>6520000000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>9761000000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>4040000000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>2686000000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>75312000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>73135000000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>71308000000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>69011000000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>66689000000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>91467000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>90031000000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>89800000000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>92344000000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>95044000000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>72605000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>73172000000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>71286000000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>75640000000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>74447000000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>2469000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>1810000000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1423000000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>1410000000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>1445000000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Tradeand Other Payables Non Current</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>1662000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>1668000000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>1628000000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>3817000000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>3732000000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>5819000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>5889000000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>6251000000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>7583000000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>7519000000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>4204000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>3667000000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>3547000000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>4031000000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>4154000000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>1615000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>2222000000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>2704000000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>3552000000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>3365000000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>62655000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>63805000000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>61984000000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>62830000000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>61751000000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>13000000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>62655000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>63805000000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>61984000000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>62823000000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>61744000000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>18862000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>16859000000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>18514000000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>16704000000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>20597000000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>1228000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>682000000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>663000000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>795000000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>992000000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>10038000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>9188000000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>9469000000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>10305000000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>10303000000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>10038000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>9188000000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>9469000000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>10305000000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>10303000000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>2252000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>2252000000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>3152000000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>1399000000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>5531000000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>26000000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>2252000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>2252000000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>3152000000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>1396000000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>5527000000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>2252000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>2252000000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>3152000000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>900000000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>1650000000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Commercial Paper</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n"/>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="n">
+        <v>496000000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>3877000000</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>3992000000</v>
+      </c>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>1134000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>864000000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>2129000000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>1719000000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>1266000000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>4210000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>3873000000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>3101000000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>2486000000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>2505000000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>656000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>673000000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>620000000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>644000000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>562000000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Interest Payable</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>656000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>673000000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>620000000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>644000000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>562000000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>3554000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>3200000000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>2481000000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>1842000000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>1943000000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>1217000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>1088000000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>921000000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>410000000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>646000000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>2337000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>2112000000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>1560000000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>1432000000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>1297000000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>179158000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>169903000000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>171092000000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>165621000000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>164630000000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>136945000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>137841000000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>139519000000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>140623000000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>142449000000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>8023000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>7139000000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>6915000000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>6027000000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>5793000000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>126134000000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>128103000000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>130074000000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>132145000000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>134194000000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>28333000000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>30302000000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>32273000000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>34344000000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>36393000000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>97801000000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>97801000000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>97801000000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>97801000000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>97801000000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>2788000000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>2599000000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>2530000000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>2451000000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>2462000000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n"/>
+      <c r="C55" s="3" t="n"/>
+      <c r="D55" s="3" t="n">
+        <v>-4896000000</v>
+      </c>
+      <c r="E55" s="3" t="n"/>
+      <c r="F55" s="3" t="n"/>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n">
+        <v>-4504000000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n"/>
+      <c r="C56" s="3" t="n"/>
+      <c r="D56" s="3" t="n">
+        <v>7426000000</v>
+      </c>
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="3" t="n"/>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n">
+        <v>7025000000</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n"/>
+      <c r="C57" s="3" t="n"/>
+      <c r="D57" s="3" t="n">
+        <v>78000000</v>
+      </c>
+      <c r="E57" s="3" t="n"/>
+      <c r="F57" s="3" t="n"/>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n">
+        <v>57000000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n"/>
+      <c r="C58" s="3" t="n"/>
+      <c r="D58" s="3" t="n">
+        <v>5656000000</v>
+      </c>
+      <c r="E58" s="3" t="n"/>
+      <c r="F58" s="3" t="n"/>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n">
+        <v>5246000000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n"/>
+      <c r="C59" s="3" t="n"/>
+      <c r="D59" s="3" t="n">
+        <v>1488000000</v>
+      </c>
+      <c r="E59" s="3" t="n"/>
+      <c r="F59" s="3" t="n"/>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n">
+        <v>1518000000</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n"/>
+      <c r="C60" s="3" t="n"/>
+      <c r="D60" s="3" t="n">
+        <v>204000000</v>
+      </c>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n">
+        <v>204000000</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n"/>
+      <c r="C61" s="3" t="n"/>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3" t="n"/>
+      <c r="F61" s="3" t="n"/>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>42213000000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>32062000000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>31573000000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>24998000000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>22181000000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>369000000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>289000000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>457000000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>656000000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>959000000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>1140000000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>641000000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>518000000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>793000000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>936000000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>4328000000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>2962000000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>2270000000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>2180000000</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>2017000000</v>
+      </c>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Finished Goods</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>1858000000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>842000000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>682000000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>477000000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Work In Process</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>1801000000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>1544000000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>1280000000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>1349000000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>1119000000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Raw Materials</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>669000000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>576000000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>308000000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>354000000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>398000000</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>16748000000</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>13996000000</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>12150000000</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>10651000000</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>8797000000</v>
+      </c>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>5918000000</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>5536000000</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>5005000000</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>4157000000</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>3234000000</v>
+      </c>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>10830000000</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>8460000000</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>7145000000</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>6494000000</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>5563000000</v>
+      </c>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n"/>
+      <c r="C72" s="3" t="n"/>
+      <c r="D72" s="3" t="n">
+        <v>-74000000</v>
+      </c>
+      <c r="E72" s="3" t="n"/>
+      <c r="F72" s="3" t="n"/>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n">
+        <v>-101000000</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n"/>
+      <c r="C73" s="3" t="n"/>
+      <c r="D73" s="3" t="n">
+        <v>7219000000</v>
+      </c>
+      <c r="E73" s="3" t="n"/>
+      <c r="F73" s="3" t="n"/>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="3" t="n">
+        <v>4517000000</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>19628000000</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>14174000000</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>16178000000</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>10718000000</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>9472000000</v>
+      </c>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>19628000000</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>14174000000</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>16178000000</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>10718000000</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>9472000000</v>
+      </c>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6236,7 +8016,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7656,13 +9436,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7684,1810 +9464,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gross margin basis</t>
+          <t>Gross margin</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FY Summary uses GAAP gross margin (~68%). Non-GAAP ~77% (Q2 FY26 77.1%) excludes amortization of acquired (VMware) intangibles in COGS. Watchlist 'Gross Mgn %' 76.3% is the non-GAAP/info.grossMargins basis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Operating income line</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Uses yfinance 'Operating Income'; 'Total Operating Income As Reported' is ~$0.6B lower (FY25 25,484 vs 26,075) — item classification.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H75"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>2025-04-30</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>2025-01-31</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>2024-10-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Ordinary Shares Number</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>4758000000</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>4736000000</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>4741000000</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>4722000000</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>4703000000</v>
-      </c>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Share Issued</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>4758000000</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>4736000000</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>4741000000</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>4722000000</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>4703000000</v>
-      </c>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Net Debt</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>45279000000</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>51883000000</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>48958000000</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>53501000000</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>57799000000</v>
-      </c>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Total Debt</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>64907000000</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>66057000000</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>65136000000</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>64229000000</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>67282000000</v>
-      </c>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Tangible Book Value</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>-38443000000</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>-48231000000</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>-48782000000</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>-58868000000</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>-64608000000</v>
-      </c>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Invested Capital</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>152598000000</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>145929000000</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>146428000000</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>137496000000</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>136857000000</v>
-      </c>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Working Capital</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>23351000000</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>15203000000</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>13059000000</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>8294000000</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>1584000000</v>
-      </c>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Net Tangible Assets</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>-38443000000</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>-48231000000</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>-48782000000</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>-58868000000</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>-64608000000</v>
-      </c>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Capital Lease Obligations</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>11000000</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>39000000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Common Stock Equity</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>87691000000</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>79872000000</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>81292000000</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>73277000000</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>69586000000</v>
-      </c>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Total Capitalization</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>150346000000</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>143677000000</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>143276000000</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>136100000000</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>131330000000</v>
-      </c>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="3" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Total Equity Gross Minority Interest</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>87691000000</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>79872000000</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>81292000000</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>73277000000</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>69586000000</v>
-      </c>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Stockholders Equity</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>87691000000</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>79872000000</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>81292000000</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>73277000000</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>69586000000</v>
-      </c>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Gains Losses Not Affecting Retained Earnings</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>208000000</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>212000000</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>218000000</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>221000000</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>206000000</v>
-      </c>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Other Equity Adjustments</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>208000000</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>212000000</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>218000000</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>221000000</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>206000000</v>
-      </c>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Retained Earnings</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>12166000000</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>6520000000</v>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>9761000000</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>4040000000</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>2686000000</v>
-      </c>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Additional Paid In Capital</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>75312000000</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>73135000000</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>71308000000</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>69011000000</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>66689000000</v>
-      </c>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Capital Stock</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Common Stock</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Preferred Stock</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Total Liabilities Net Minority Interest</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>91467000000</v>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>90031000000</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>89800000000</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>92344000000</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>95044000000</v>
-      </c>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Total Non Current Liabilities Net Minority Interest</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>72605000000</v>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>73172000000</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>71286000000</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>75640000000</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>74447000000</v>
-      </c>
-      <c r="G23" s="3" t="n"/>
-      <c r="H23" s="3" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Other Non Current Liabilities</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>2469000000</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>1810000000</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>1423000000</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>1410000000</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>1445000000</v>
-      </c>
-      <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Tradeand Other Payables Non Current</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>1662000000</v>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>1668000000</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>1628000000</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>3817000000</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>3732000000</v>
-      </c>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Non Current Deferred Liabilities</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>5819000000</v>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>5889000000</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>6251000000</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>7583000000</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>7519000000</v>
-      </c>
-      <c r="G26" s="3" t="n"/>
-      <c r="H26" s="3" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Non Current Deferred Revenue</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>4204000000</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>3667000000</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>3547000000</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>4031000000</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>4154000000</v>
-      </c>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Non Current Deferred Taxes Liabilities</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>1615000000</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>2222000000</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>2704000000</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>3552000000</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>3365000000</v>
-      </c>
-      <c r="G28" s="3" t="n"/>
-      <c r="H28" s="3" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Long Term Debt And Capital Lease Obligation</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>62655000000</v>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>63805000000</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>61984000000</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>62830000000</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>61751000000</v>
-      </c>
-      <c r="G29" s="3" t="n"/>
-      <c r="H29" s="3" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Long Term Capital Lease Obligation</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>11000000</v>
-      </c>
-      <c r="H30" s="3" t="n">
-        <v>13000000</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Long Term Debt</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>62655000000</v>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>63805000000</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>61984000000</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>62823000000</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>61744000000</v>
-      </c>
-      <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Current Liabilities</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>18862000000</v>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>16859000000</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>18514000000</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>16704000000</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>20597000000</v>
-      </c>
-      <c r="G32" s="3" t="n"/>
-      <c r="H32" s="3" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Other Current Liabilities</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>1228000000</v>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>682000000</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>663000000</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>795000000</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>992000000</v>
-      </c>
-      <c r="G33" s="3" t="n"/>
-      <c r="H33" s="3" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Current Deferred Liabilities</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="n">
-        <v>10038000000</v>
-      </c>
-      <c r="C34" s="3" t="n">
-        <v>9188000000</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>9469000000</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>10305000000</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>10303000000</v>
-      </c>
-      <c r="G34" s="3" t="n"/>
-      <c r="H34" s="3" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Current Deferred Revenue</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="n">
-        <v>10038000000</v>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>9188000000</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>9469000000</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>10305000000</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>10303000000</v>
-      </c>
-      <c r="G35" s="3" t="n"/>
-      <c r="H35" s="3" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Current Debt And Capital Lease Obligation</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="n">
-        <v>2252000000</v>
-      </c>
-      <c r="C36" s="3" t="n">
-        <v>2252000000</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>3152000000</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>1399000000</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>5531000000</v>
-      </c>
-      <c r="G36" s="3" t="n"/>
-      <c r="H36" s="3" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Current Capital Lease Obligation</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="n"/>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>11000000</v>
-      </c>
-      <c r="H37" s="3" t="n">
-        <v>26000000</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Current Debt</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="n">
-        <v>2252000000</v>
-      </c>
-      <c r="C38" s="3" t="n">
-        <v>2252000000</v>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>3152000000</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>1396000000</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>5527000000</v>
-      </c>
-      <c r="G38" s="3" t="n"/>
-      <c r="H38" s="3" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Other Current Borrowings</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="n">
-        <v>2252000000</v>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>2252000000</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>3152000000</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>900000000</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>1650000000</v>
-      </c>
-      <c r="G39" s="3" t="n"/>
-      <c r="H39" s="3" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Commercial Paper</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="3" t="n"/>
-      <c r="E40" s="3" t="n">
-        <v>496000000</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>3877000000</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>3992000000</v>
-      </c>
-      <c r="H40" s="3" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>1134000000</v>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>864000000</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>2129000000</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>1719000000</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>1266000000</v>
-      </c>
-      <c r="G41" s="3" t="n"/>
-      <c r="H41" s="3" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Payables And Accrued Expenses</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>4210000000</v>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>3873000000</v>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>3101000000</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>2486000000</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>2505000000</v>
-      </c>
-      <c r="G42" s="3" t="n"/>
-      <c r="H42" s="3" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Current Accrued Expenses</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>656000000</v>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>673000000</v>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>620000000</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>644000000</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>562000000</v>
-      </c>
-      <c r="G43" s="3" t="n"/>
-      <c r="H43" s="3" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Interest Payable</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="n">
-        <v>656000000</v>
-      </c>
-      <c r="C44" s="3" t="n">
-        <v>673000000</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>620000000</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>644000000</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>562000000</v>
-      </c>
-      <c r="G44" s="3" t="n"/>
-      <c r="H44" s="3" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Payables</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="n">
-        <v>3554000000</v>
-      </c>
-      <c r="C45" s="3" t="n">
-        <v>3200000000</v>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>2481000000</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>1842000000</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>1943000000</v>
-      </c>
-      <c r="G45" s="3" t="n"/>
-      <c r="H45" s="3" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Total Tax Payable</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="n">
-        <v>1217000000</v>
-      </c>
-      <c r="C46" s="3" t="n">
-        <v>1088000000</v>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>921000000</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>410000000</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>646000000</v>
-      </c>
-      <c r="G46" s="3" t="n"/>
-      <c r="H46" s="3" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Accounts Payable</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="n">
-        <v>2337000000</v>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v>2112000000</v>
-      </c>
-      <c r="D47" s="3" t="n">
-        <v>1560000000</v>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>1432000000</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>1297000000</v>
-      </c>
-      <c r="G47" s="3" t="n"/>
-      <c r="H47" s="3" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Total Assets</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="n">
-        <v>179158000000</v>
-      </c>
-      <c r="C48" s="3" t="n">
-        <v>169903000000</v>
-      </c>
-      <c r="D48" s="3" t="n">
-        <v>171092000000</v>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>165621000000</v>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>164630000000</v>
-      </c>
-      <c r="G48" s="3" t="n"/>
-      <c r="H48" s="3" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Total Non Current Assets</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="n">
-        <v>136945000000</v>
-      </c>
-      <c r="C49" s="3" t="n">
-        <v>137841000000</v>
-      </c>
-      <c r="D49" s="3" t="n">
-        <v>139519000000</v>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>140623000000</v>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>142449000000</v>
-      </c>
-      <c r="G49" s="3" t="n"/>
-      <c r="H49" s="3" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Other Non Current Assets</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="n">
-        <v>8023000000</v>
-      </c>
-      <c r="C50" s="3" t="n">
-        <v>7139000000</v>
-      </c>
-      <c r="D50" s="3" t="n">
-        <v>6915000000</v>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>6027000000</v>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>5793000000</v>
-      </c>
-      <c r="G50" s="3" t="n"/>
-      <c r="H50" s="3" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Goodwill And Other Intangible Assets</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="n">
-        <v>126134000000</v>
-      </c>
-      <c r="C51" s="3" t="n">
-        <v>128103000000</v>
-      </c>
-      <c r="D51" s="3" t="n">
-        <v>130074000000</v>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>132145000000</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>134194000000</v>
-      </c>
-      <c r="G51" s="3" t="n"/>
-      <c r="H51" s="3" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Other Intangible Assets</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="n">
-        <v>28333000000</v>
-      </c>
-      <c r="C52" s="3" t="n">
-        <v>30302000000</v>
-      </c>
-      <c r="D52" s="3" t="n">
-        <v>32273000000</v>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>34344000000</v>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>36393000000</v>
-      </c>
-      <c r="G52" s="3" t="n"/>
-      <c r="H52" s="3" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Goodwill</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="n">
-        <v>97801000000</v>
-      </c>
-      <c r="C53" s="3" t="n">
-        <v>97801000000</v>
-      </c>
-      <c r="D53" s="3" t="n">
-        <v>97801000000</v>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>97801000000</v>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>97801000000</v>
-      </c>
-      <c r="G53" s="3" t="n"/>
-      <c r="H53" s="3" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Net PPE</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="n">
-        <v>2788000000</v>
-      </c>
-      <c r="C54" s="3" t="n">
-        <v>2599000000</v>
-      </c>
-      <c r="D54" s="3" t="n">
-        <v>2530000000</v>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>2451000000</v>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>2462000000</v>
-      </c>
-      <c r="G54" s="3" t="n"/>
-      <c r="H54" s="3" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Accumulated Depreciation</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="n"/>
-      <c r="C55" s="3" t="n"/>
-      <c r="D55" s="3" t="n">
-        <v>-4896000000</v>
-      </c>
-      <c r="E55" s="3" t="n"/>
-      <c r="F55" s="3" t="n"/>
-      <c r="G55" s="3" t="n"/>
-      <c r="H55" s="3" t="n">
-        <v>-4504000000</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Gross PPE</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="n"/>
-      <c r="C56" s="3" t="n"/>
-      <c r="D56" s="3" t="n">
-        <v>7426000000</v>
-      </c>
-      <c r="E56" s="3" t="n"/>
-      <c r="F56" s="3" t="n"/>
-      <c r="G56" s="3" t="n"/>
-      <c r="H56" s="3" t="n">
-        <v>7025000000</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Construction In Progress</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="n"/>
-      <c r="C57" s="3" t="n"/>
-      <c r="D57" s="3" t="n">
-        <v>78000000</v>
-      </c>
-      <c r="E57" s="3" t="n"/>
-      <c r="F57" s="3" t="n"/>
-      <c r="G57" s="3" t="n"/>
-      <c r="H57" s="3" t="n">
-        <v>57000000</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Machinery Furniture Equipment</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="n"/>
-      <c r="C58" s="3" t="n"/>
-      <c r="D58" s="3" t="n">
-        <v>5656000000</v>
-      </c>
-      <c r="E58" s="3" t="n"/>
-      <c r="F58" s="3" t="n"/>
-      <c r="G58" s="3" t="n"/>
-      <c r="H58" s="3" t="n">
-        <v>5246000000</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Buildings And Improvements</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="n"/>
-      <c r="C59" s="3" t="n"/>
-      <c r="D59" s="3" t="n">
-        <v>1488000000</v>
-      </c>
-      <c r="E59" s="3" t="n"/>
-      <c r="F59" s="3" t="n"/>
-      <c r="G59" s="3" t="n"/>
-      <c r="H59" s="3" t="n">
-        <v>1518000000</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Land And Improvements</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="n"/>
-      <c r="C60" s="3" t="n"/>
-      <c r="D60" s="3" t="n">
-        <v>204000000</v>
-      </c>
-      <c r="E60" s="3" t="n"/>
-      <c r="F60" s="3" t="n"/>
-      <c r="G60" s="3" t="n"/>
-      <c r="H60" s="3" t="n">
-        <v>204000000</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Properties</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="n"/>
-      <c r="C61" s="3" t="n"/>
-      <c r="D61" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="3" t="n"/>
-      <c r="F61" s="3" t="n"/>
-      <c r="G61" s="3" t="n"/>
-      <c r="H61" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Current Assets</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="n">
-        <v>42213000000</v>
-      </c>
-      <c r="C62" s="3" t="n">
-        <v>32062000000</v>
-      </c>
-      <c r="D62" s="3" t="n">
-        <v>31573000000</v>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>24998000000</v>
-      </c>
-      <c r="F62" s="3" t="n">
-        <v>22181000000</v>
-      </c>
-      <c r="G62" s="3" t="n"/>
-      <c r="H62" s="3" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Other Current Assets</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="n">
-        <v>369000000</v>
-      </c>
-      <c r="C63" s="3" t="n">
-        <v>289000000</v>
-      </c>
-      <c r="D63" s="3" t="n">
-        <v>457000000</v>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>656000000</v>
-      </c>
-      <c r="F63" s="3" t="n">
-        <v>959000000</v>
-      </c>
-      <c r="G63" s="3" t="n"/>
-      <c r="H63" s="3" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Prepaid Assets</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="n">
-        <v>1140000000</v>
-      </c>
-      <c r="C64" s="3" t="n">
-        <v>641000000</v>
-      </c>
-      <c r="D64" s="3" t="n">
-        <v>518000000</v>
-      </c>
-      <c r="E64" s="3" t="n">
-        <v>793000000</v>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>936000000</v>
-      </c>
-      <c r="G64" s="3" t="n"/>
-      <c r="H64" s="3" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="n">
-        <v>4328000000</v>
-      </c>
-      <c r="C65" s="3" t="n">
-        <v>2962000000</v>
-      </c>
-      <c r="D65" s="3" t="n">
-        <v>2270000000</v>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v>2180000000</v>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>2017000000</v>
-      </c>
-      <c r="G65" s="3" t="n"/>
-      <c r="H65" s="3" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Finished Goods</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="n">
-        <v>1858000000</v>
-      </c>
-      <c r="C66" s="3" t="n">
-        <v>842000000</v>
-      </c>
-      <c r="D66" s="3" t="n">
-        <v>682000000</v>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>477000000</v>
-      </c>
-      <c r="F66" s="3" t="n">
-        <v>500000000</v>
-      </c>
-      <c r="G66" s="3" t="n"/>
-      <c r="H66" s="3" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Work In Process</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="n">
-        <v>1801000000</v>
-      </c>
-      <c r="C67" s="3" t="n">
-        <v>1544000000</v>
-      </c>
-      <c r="D67" s="3" t="n">
-        <v>1280000000</v>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>1349000000</v>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>1119000000</v>
-      </c>
-      <c r="G67" s="3" t="n"/>
-      <c r="H67" s="3" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Raw Materials</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="n">
-        <v>669000000</v>
-      </c>
-      <c r="C68" s="3" t="n">
-        <v>576000000</v>
-      </c>
-      <c r="D68" s="3" t="n">
-        <v>308000000</v>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>354000000</v>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>398000000</v>
-      </c>
-      <c r="G68" s="3" t="n"/>
-      <c r="H68" s="3" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Receivables</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="n">
-        <v>16748000000</v>
-      </c>
-      <c r="C69" s="3" t="n">
-        <v>13996000000</v>
-      </c>
-      <c r="D69" s="3" t="n">
-        <v>12150000000</v>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>10651000000</v>
-      </c>
-      <c r="F69" s="3" t="n">
-        <v>8797000000</v>
-      </c>
-      <c r="G69" s="3" t="n"/>
-      <c r="H69" s="3" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Other Receivables</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="n">
-        <v>5918000000</v>
-      </c>
-      <c r="C70" s="3" t="n">
-        <v>5536000000</v>
-      </c>
-      <c r="D70" s="3" t="n">
-        <v>5005000000</v>
-      </c>
-      <c r="E70" s="3" t="n">
-        <v>4157000000</v>
-      </c>
-      <c r="F70" s="3" t="n">
-        <v>3234000000</v>
-      </c>
-      <c r="G70" s="3" t="n"/>
-      <c r="H70" s="3" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="n">
-        <v>10830000000</v>
-      </c>
-      <c r="C71" s="3" t="n">
-        <v>8460000000</v>
-      </c>
-      <c r="D71" s="3" t="n">
-        <v>7145000000</v>
-      </c>
-      <c r="E71" s="3" t="n">
-        <v>6494000000</v>
-      </c>
-      <c r="F71" s="3" t="n">
-        <v>5563000000</v>
-      </c>
-      <c r="G71" s="3" t="n"/>
-      <c r="H71" s="3" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Allowance For Doubtful Accounts Receivable</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="n"/>
-      <c r="C72" s="3" t="n"/>
-      <c r="D72" s="3" t="n">
-        <v>-74000000</v>
-      </c>
-      <c r="E72" s="3" t="n"/>
-      <c r="F72" s="3" t="n"/>
-      <c r="G72" s="3" t="n"/>
-      <c r="H72" s="3" t="n">
-        <v>-101000000</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Gross Accounts Receivable</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="n"/>
-      <c r="C73" s="3" t="n"/>
-      <c r="D73" s="3" t="n">
-        <v>7219000000</v>
-      </c>
-      <c r="E73" s="3" t="n"/>
-      <c r="F73" s="3" t="n"/>
-      <c r="G73" s="3" t="n"/>
-      <c r="H73" s="3" t="n">
-        <v>4517000000</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Cash Cash Equivalents And Short Term Investments</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="n">
-        <v>19628000000</v>
-      </c>
-      <c r="C74" s="3" t="n">
-        <v>14174000000</v>
-      </c>
-      <c r="D74" s="3" t="n">
-        <v>16178000000</v>
-      </c>
-      <c r="E74" s="3" t="n">
-        <v>10718000000</v>
-      </c>
-      <c r="F74" s="3" t="n">
-        <v>9472000000</v>
-      </c>
-      <c r="G74" s="3" t="n"/>
-      <c r="H74" s="3" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Cash And Cash Equivalents</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="n">
-        <v>19628000000</v>
-      </c>
-      <c r="C75" s="3" t="n">
-        <v>14174000000</v>
-      </c>
-      <c r="D75" s="3" t="n">
-        <v>16178000000</v>
-      </c>
-      <c r="E75" s="3" t="n">
-        <v>10718000000</v>
-      </c>
-      <c r="F75" s="3" t="n">
-        <v>9472000000</v>
-      </c>
-      <c r="G75" s="3" t="n"/>
-      <c r="H75" s="3" t="n"/>
+          <t>GAAP (statement) ~68% vs yfinance info.grossMargins 76% — info is a non-GAAP basis; FY Summary uses GAAP</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/per-stock/AVGO/financials.xlsx
+++ b/per-stock/AVGO/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2013133668352</v>
+        <v>1957030658048</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2065016553472</v>
+        <v>2002309611520</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>82.721794</v>
+        <v>68.44426</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23.247448</v>
+        <v>21.220005</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29.482641</v>
+        <v>25.932959</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -606,7 +615,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.76725996</v>
+        <v>0.76284</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -621,7 +630,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.44943002</v>
+        <v>0.48988</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -636,7 +645,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.36571997</v>
+        <v>0.38848</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -651,7 +660,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.33370999</v>
+        <v>0.37280998</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -666,7 +675,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.295</v>
+        <v>0.479</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -681,7 +690,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14174000128</v>
+        <v>19627999232</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -696,7 +705,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>66056998912</v>
+        <v>64907001856</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -711,11 +720,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25503750144</v>
+        <v>32762000000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -726,7 +735,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4734668184</v>
+        <v>4757580198</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -741,7 +750,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>425.19</v>
+        <v>411.35</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -785,6 +794,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-04-30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D50</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C50</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B50</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B46:E46)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D48</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C48</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B48</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B44:E44)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D40</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C40</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B40</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B36:E36)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D7</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B7</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B7:E7)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D6</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C6</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B6</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B4</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D4/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C4/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B4/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1834,13 +2314,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1850,6 +2330,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1860,30 +2341,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-10-31</t>
         </is>
@@ -1896,21 +2382,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-5747285.291214</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-10633068.944478</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>-34230000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>-40513718.070009</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>-2029498.525074</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>-36120000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1919,21 +2406,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.08094800000000001</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.103234</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.21</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.216651</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>0.023599</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>0.21</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1942,21 +2430,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>13142000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>11252000000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>10026000000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>8481000000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>8106000000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>8709000000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1965,21 +2454,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>-71000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>-103000000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>-163000000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>-187000000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>-86000000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>-172000000</v>
-      </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1988,21 +2478,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-71000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-103000000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>-163000000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>-187000000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>-86000000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>-172000000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2011,21 +2502,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>9310000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>7349000000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>8518000000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>4140000000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>4965000000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>5503000000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2034,21 +2526,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>2165000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>2153000000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>2233000000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>2202000000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>2166000000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>2174000000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2057,21 +2550,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>5113000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>4508000000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>4040000000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>3554000000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>3147000000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>3108000000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2080,21 +2574,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>13071000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>11149000000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>9863000000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>8294000000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>8020000000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>8537000000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2103,21 +2598,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>10906000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>8996000000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>7630000000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>6092000000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>5854000000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>6363000000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2126,21 +2622,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-776000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-801000000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-414000000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-807000000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-769000000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-873000000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2149,21 +2646,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>776000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>801000000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>761000000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>807000000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>769000000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>873000000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2172,21 +2670,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>9375252714.708786</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>7441366931.055522</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>8646770000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>4286486281.929991</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>5048970501.474926</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>5638880000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2195,21 +2694,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>9310000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>7349000000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>8518000000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>4140000000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>4965000000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>5503000000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2218,21 +2718,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>11328000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>10645000000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>10361000000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>9878000000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>9089000000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>8484000000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2241,21 +2742,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>10788000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>8563000000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>7508000000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>5887000000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>5829000000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>6260000000</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2264,21 +2766,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>4876000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>4888000000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>4889000000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>4860000000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>4826000000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>4836000000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2287,21 +2790,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>4747000000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>4741000000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>4732000000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>4714000000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>4707000000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>4695000000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2310,21 +2814,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>1.74</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>0.85</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>1.03</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>1.14</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2333,21 +2838,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>1.55</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>0.88</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>1.17</v>
-      </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2356,21 +2862,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>9310000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>7349000000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>8518000000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>4140000000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>4965000000</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>5503000000</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2379,21 +2886,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>9310000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>7349000000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>8518000000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>4140000000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>4965000000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>5503000000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2402,21 +2910,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>9310000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>7349000000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>8518000000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>4140000000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>4965000000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>5503000000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2425,21 +2934,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>9310000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>7349000000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>8518000000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>4140000000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>4965000000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>5503000000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2448,9 +2958,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="n">
         <v>0</v>
       </c>
@@ -2461,6 +2969,9 @@
         <v>0</v>
       </c>
       <c r="G26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3" t="n">
         <v>119000000</v>
       </c>
     </row>
@@ -2471,21 +2982,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>9310000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>7349000000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>8518000000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>4140000000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>4965000000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>5503000000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2494,21 +3006,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>820000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>846000000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>-1649000000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>1145000000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>120000000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>-13000000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2517,21 +3030,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>10130000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>8195000000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>6869000000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>5285000000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>5085000000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>5490000000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2540,21 +3054,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>47000000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>330000000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>-371000000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>18000000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>-61000000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>-69000000</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2563,21 +3078,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>118000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>433000000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>-208000000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>205000000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>25000000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>103000000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2586,21 +3102,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>-71000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>-103000000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>-146000000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>-187000000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>-86000000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>-172000000</v>
-      </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2609,21 +3126,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>71000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>103000000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>146000000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>187000000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>86000000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>172000000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2632,21 +3150,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>-776000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>-801000000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>-414000000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>-807000000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>-769000000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>-873000000</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2655,21 +3174,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>776000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>801000000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>761000000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>807000000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>769000000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>873000000</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2678,21 +3198,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>10859000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>8666000000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>7654000000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>6074000000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>5915000000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>6432000000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2701,21 +3222,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>4556000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>4491000000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>4595000000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>4629000000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>4282000000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>3713000000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2724,7 +3246,7 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>507000000</v>
+        <v>506000000</v>
       </c>
       <c r="C38" s="3" t="n">
         <v>507000000</v>
@@ -2733,12 +3255,13 @@
         <v>507000000</v>
       </c>
       <c r="E38" s="3" t="n">
+        <v>507000000</v>
+      </c>
+      <c r="F38" s="3" t="n">
         <v>506000000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>511000000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2747,7 +3270,7 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>507000000</v>
+        <v>506000000</v>
       </c>
       <c r="C39" s="3" t="n">
         <v>507000000</v>
@@ -2756,12 +3279,13 @@
         <v>507000000</v>
       </c>
       <c r="E39" s="3" t="n">
+        <v>507000000</v>
+      </c>
+      <c r="F39" s="3" t="n">
         <v>506000000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>511000000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2770,7 +3294,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>507000000</v>
+        <v>506000000</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>507000000</v>
@@ -2779,12 +3303,13 @@
         <v>507000000</v>
       </c>
       <c r="E40" s="3" t="n">
+        <v>507000000</v>
+      </c>
+      <c r="F40" s="3" t="n">
         <v>506000000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>511000000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2793,7 +3318,7 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>507000000</v>
+        <v>506000000</v>
       </c>
       <c r="C41" s="3" t="n">
         <v>507000000</v>
@@ -2802,12 +3327,13 @@
         <v>507000000</v>
       </c>
       <c r="E41" s="3" t="n">
+        <v>507000000</v>
+      </c>
+      <c r="F41" s="3" t="n">
         <v>506000000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>511000000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2816,21 +3342,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>2995000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>2965000000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>2981000000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>3050000000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>2693000000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>2253000000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2839,21 +3366,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>1055000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>1019000000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>1107000000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>1072000000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>1083000000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>949000000</v>
-      </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2862,21 +3390,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>15415000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>13157000000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>12249000000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>10703000000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>10197000000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>10145000000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2885,21 +3414,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>6772000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>6154000000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>5766000000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>5249000000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>4807000000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>4771000000</v>
-      </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2908,21 +3438,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>22187000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>19311000000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>18015000000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>15952000000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>15004000000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>14916000000</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2931,28 +3462,29 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>22187000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>19311000000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>18015000000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>15952000000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>15004000000</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>14916000000</v>
-      </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4425,13 +4957,19 @@
           <t>Allowance For Doubtful Accounts Receivable</t>
         </is>
       </c>
-      <c r="B74" s="3" t="n"/>
-      <c r="C74" s="3" t="n"/>
-      <c r="D74" s="3" t="n"/>
-      <c r="E74" s="3" t="n"/>
-      <c r="F74" s="3" t="n">
-        <v>-2597000000</v>
-      </c>
+      <c r="B74" s="3" t="n">
+        <v>-74000000</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>-101000000</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>-137000000</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>-126000000</v>
+      </c>
+      <c r="F74" s="3" t="n"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4439,13 +4977,19 @@
           <t>Gross Accounts Receivable</t>
         </is>
       </c>
-      <c r="B75" s="3" t="n"/>
-      <c r="C75" s="3" t="n"/>
-      <c r="D75" s="3" t="n"/>
-      <c r="E75" s="3" t="n"/>
-      <c r="F75" s="3" t="n">
-        <v>4668000000</v>
-      </c>
+      <c r="B75" s="3" t="n">
+        <v>7219000000</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>4517000000</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>3291000000</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>3084000000</v>
+      </c>
+      <c r="F75" s="3" t="n"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4492,13 +5036,1797 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:H75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>4758000000</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>4736000000</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>4741000000</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>4722000000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>4703000000</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>4758000000</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>4736000000</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>4741000000</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>4722000000</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>4703000000</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>45279000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>51883000000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>48958000000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>53501000000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>57799000000</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>64907000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>66057000000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>65136000000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>64229000000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>67282000000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>-38443000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>-48231000000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>-48782000000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>-58868000000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>-64608000000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>152598000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>145929000000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>146428000000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>137496000000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>136857000000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>23351000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>15203000000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>13059000000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>8294000000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1584000000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>-38443000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>-48231000000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>-48782000000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-58868000000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>-64608000000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>39000000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>87691000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>79872000000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>81292000000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>73277000000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>69586000000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>150346000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>143677000000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>143276000000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>136100000000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>131330000000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>87691000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>79872000000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>81292000000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>73277000000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>69586000000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>87691000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>79872000000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>81292000000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>73277000000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>69586000000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>208000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>212000000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>218000000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>221000000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>206000000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>208000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>212000000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>218000000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>221000000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>206000000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>12166000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>6520000000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>9761000000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>4040000000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>2686000000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>75312000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>73135000000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>71308000000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>69011000000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>66689000000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>91467000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>90031000000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>89800000000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>92344000000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>95044000000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>72605000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>73172000000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>71286000000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>75640000000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>74447000000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>2469000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>1810000000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1423000000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>1410000000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>1445000000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Tradeand Other Payables Non Current</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>1662000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>1668000000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>1628000000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>3817000000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>3732000000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>5819000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>5889000000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>6251000000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>7583000000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>7519000000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>4204000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>3667000000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>3547000000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>4031000000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>4154000000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>1615000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>2222000000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>2704000000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>3552000000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>3365000000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>62655000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>63805000000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>61984000000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>62830000000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>61751000000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>13000000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>62655000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>63805000000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>61984000000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>62823000000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>61744000000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>18862000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>16859000000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>18514000000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>16704000000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>20597000000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>1228000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>682000000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>663000000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>795000000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>992000000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>10038000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>9188000000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>9469000000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>10305000000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>10303000000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>10038000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>9188000000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>9469000000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>10305000000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>10303000000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>2252000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>2252000000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>3152000000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>1399000000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>5531000000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>26000000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>2252000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>2252000000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>3152000000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>1396000000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>5527000000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>2252000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>2252000000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>3152000000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>900000000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>1650000000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Commercial Paper</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n"/>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="n">
+        <v>496000000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>3877000000</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>3992000000</v>
+      </c>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>1134000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>864000000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>2129000000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>1719000000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>1266000000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>4210000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>3873000000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>3101000000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>2486000000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>2505000000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>656000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>673000000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>620000000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>644000000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>562000000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Interest Payable</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>656000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>673000000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>620000000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>644000000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>562000000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>3554000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>3200000000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>2481000000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>1842000000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>1943000000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>1217000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>1088000000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>921000000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>410000000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>646000000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>2337000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>2112000000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>1560000000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>1432000000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>1297000000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>179158000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>169903000000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>171092000000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>165621000000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>164630000000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>136945000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>137841000000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>139519000000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>140623000000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>142449000000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>8023000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>7139000000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>6915000000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>6027000000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>5793000000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>126134000000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>128103000000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>130074000000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>132145000000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>134194000000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>28333000000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>30302000000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>32273000000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>34344000000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>36393000000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>97801000000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>97801000000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>97801000000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>97801000000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>97801000000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>2788000000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>2599000000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>2530000000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>2451000000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>2462000000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n"/>
+      <c r="C55" s="3" t="n"/>
+      <c r="D55" s="3" t="n">
+        <v>-4896000000</v>
+      </c>
+      <c r="E55" s="3" t="n"/>
+      <c r="F55" s="3" t="n"/>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n">
+        <v>-4504000000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n"/>
+      <c r="C56" s="3" t="n"/>
+      <c r="D56" s="3" t="n">
+        <v>7426000000</v>
+      </c>
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="3" t="n"/>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n">
+        <v>7025000000</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n"/>
+      <c r="C57" s="3" t="n"/>
+      <c r="D57" s="3" t="n">
+        <v>78000000</v>
+      </c>
+      <c r="E57" s="3" t="n"/>
+      <c r="F57" s="3" t="n"/>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n">
+        <v>57000000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n"/>
+      <c r="C58" s="3" t="n"/>
+      <c r="D58" s="3" t="n">
+        <v>5656000000</v>
+      </c>
+      <c r="E58" s="3" t="n"/>
+      <c r="F58" s="3" t="n"/>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n">
+        <v>5246000000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n"/>
+      <c r="C59" s="3" t="n"/>
+      <c r="D59" s="3" t="n">
+        <v>1488000000</v>
+      </c>
+      <c r="E59" s="3" t="n"/>
+      <c r="F59" s="3" t="n"/>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n">
+        <v>1518000000</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n"/>
+      <c r="C60" s="3" t="n"/>
+      <c r="D60" s="3" t="n">
+        <v>204000000</v>
+      </c>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n">
+        <v>204000000</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n"/>
+      <c r="C61" s="3" t="n"/>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3" t="n"/>
+      <c r="F61" s="3" t="n"/>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>42213000000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>32062000000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>31573000000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>24998000000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>22181000000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>369000000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>289000000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>457000000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>656000000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>959000000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>1140000000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>641000000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>518000000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>793000000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>936000000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>4328000000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>2962000000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>2270000000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>2180000000</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>2017000000</v>
+      </c>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Finished Goods</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>1858000000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>842000000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>682000000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>477000000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Work In Process</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>1801000000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>1544000000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>1280000000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>1349000000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>1119000000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Raw Materials</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>669000000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>576000000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>308000000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>354000000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>398000000</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>16748000000</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>13996000000</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>12150000000</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>10651000000</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>8797000000</v>
+      </c>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>5918000000</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>5536000000</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>5005000000</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>4157000000</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>3234000000</v>
+      </c>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>10830000000</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>8460000000</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>7145000000</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>6494000000</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>5563000000</v>
+      </c>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n"/>
+      <c r="C72" s="3" t="n"/>
+      <c r="D72" s="3" t="n">
+        <v>-74000000</v>
+      </c>
+      <c r="E72" s="3" t="n"/>
+      <c r="F72" s="3" t="n"/>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n">
+        <v>-101000000</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n"/>
+      <c r="C73" s="3" t="n"/>
+      <c r="D73" s="3" t="n">
+        <v>7219000000</v>
+      </c>
+      <c r="E73" s="3" t="n"/>
+      <c r="F73" s="3" t="n"/>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="3" t="n">
+        <v>4517000000</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>19628000000</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>14174000000</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>16178000000</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>10718000000</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>9472000000</v>
+      </c>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>19628000000</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>14174000000</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>16178000000</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>10718000000</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>9472000000</v>
+      </c>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4844,21 +7172,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Net Preferred Stock Issuance</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>Common Stock Dividend Paid</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-11142000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-9814000000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-7645000000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-7032000000</v>
+      </c>
+      <c r="F17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Preferred Stock Issuance</t>
+          <t>Net Preferred Stock Issuance</t>
         </is>
       </c>
       <c r="B18" s="3" t="n"/>
@@ -4872,87 +7206,81 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Net Common Stock Issuance</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>-6089000000</v>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>-12202000000</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>-7563000000</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>-8341000000</v>
-      </c>
-      <c r="F19" s="3" t="n"/>
+          <t>Preferred Stock Issuance</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Common Stock Payments</t>
+          <t>Net Common Stock Issuance</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-6310000000</v>
+        <v>-6089000000</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-12392000000</v>
+        <v>-12202000000</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-7685000000</v>
+        <v>-7563000000</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-8455000000</v>
+        <v>-8341000000</v>
       </c>
       <c r="F20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Common Stock Issuance</t>
+          <t>Common Stock Payments</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>221000000</v>
+        <v>-6310000000</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>190000000</v>
+        <v>-12392000000</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>122000000</v>
+        <v>-7685000000</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>114000000</v>
+        <v>-8455000000</v>
       </c>
       <c r="F21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Net Issuance Payments Of Debt</t>
+          <t>Common Stock Issuance</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-2812000000</v>
+        <v>221000000</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>20346000000</v>
+        <v>190000000</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>-403000000</v>
+        <v>122000000</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>-426000000</v>
+        <v>114000000</v>
       </c>
       <c r="F22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Net Long Term Debt Issuance</t>
+          <t>Net Issuance Payments Of Debt</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
@@ -4972,67 +7300,67 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Long Term Debt Payments</t>
+          <t>Net Long Term Debt Issuance</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>-18478000000</v>
+        <v>-2812000000</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>-19608000000</v>
+        <v>20346000000</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>-403000000</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>-2361000000</v>
+        <v>-426000000</v>
       </c>
       <c r="F24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Long Term Debt Issuance</t>
+          <t>Long Term Debt Payments</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>15666000000</v>
+        <v>-18478000000</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>39954000000</v>
+        <v>-19608000000</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0</v>
+        <v>-403000000</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>1935000000</v>
+        <v>-2361000000</v>
       </c>
       <c r="F25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Investing Cash Flow</t>
+          <t>Long Term Debt Issuance</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-580000000</v>
+        <v>15666000000</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-23070000000</v>
+        <v>39954000000</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-689000000</v>
+        <v>0</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-667000000</v>
+        <v>1935000000</v>
       </c>
       <c r="F26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cash Flow From Continuing Investing Activities</t>
+          <t>Investing Cash Flow</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
@@ -5052,221 +7380,221 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Net Other Investing Changes</t>
+          <t>Cash Flow From Continuing Investing Activities</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>92000000</v>
+        <v>-580000000</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>-10000000</v>
+        <v>-23070000000</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>-66000000</v>
+        <v>-689000000</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>3000000</v>
+        <v>-667000000</v>
       </c>
       <c r="F28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Net Investment Purchase And Sale</t>
+          <t>Net Other Investing Changes</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-349000000</v>
+        <v>92000000</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-19000000</v>
+        <v>-10000000</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-118000000</v>
+        <v>-66000000</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0</v>
+        <v>3000000</v>
       </c>
       <c r="F29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sale Of Investment</t>
+          <t>Net Investment Purchase And Sale</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>248000000</v>
+        <v>-349000000</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>156000000</v>
+        <v>-19000000</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>228000000</v>
+        <v>-118000000</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>200000000</v>
+        <v>0</v>
       </c>
       <c r="F30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Purchase Of Investment</t>
+          <t>Sale Of Investment</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-597000000</v>
+        <v>248000000</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-175000000</v>
+        <v>156000000</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-346000000</v>
+        <v>228000000</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-200000000</v>
+        <v>200000000</v>
       </c>
       <c r="F31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Net Business Purchase And Sale</t>
+          <t>Purchase Of Investment</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>300000000</v>
+        <v>-597000000</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>-22493000000</v>
+        <v>-175000000</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>-53000000</v>
+        <v>-346000000</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>-246000000</v>
+        <v>-200000000</v>
       </c>
       <c r="F32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sale Of Business</t>
+          <t>Net Business Purchase And Sale</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
         <v>300000000</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>3485000000</v>
+        <v>-22493000000</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>0</v>
+        <v>-53000000</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>0</v>
+        <v>-246000000</v>
       </c>
       <c r="F33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Purchase Of Business</t>
+          <t>Sale Of Business</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>300000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>3485000000</v>
+      </c>
+      <c r="D34" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C34" s="3" t="n">
-        <v>-25978000000</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>-53000000</v>
-      </c>
       <c r="E34" s="3" t="n">
-        <v>-246000000</v>
+        <v>0</v>
       </c>
       <c r="F34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Net PPE Purchase And Sale</t>
+          <t>Purchase Of Business</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>-623000000</v>
+        <v>0</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-548000000</v>
+        <v>-25978000000</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-452000000</v>
+        <v>-53000000</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-424000000</v>
+        <v>-246000000</v>
       </c>
       <c r="F35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sale Of PPE</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="n"/>
-      <c r="E36" s="3" t="n"/>
-      <c r="F36" s="3" t="n">
-        <v>4000000</v>
-      </c>
+          <t>Net PPE Purchase And Sale</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>-623000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>-548000000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>-452000000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>-424000000</v>
+      </c>
+      <c r="F36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Purchase Of PPE</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>-623000000</v>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>-548000000</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>-452000000</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>-424000000</v>
-      </c>
-      <c r="F37" s="3" t="n"/>
+          <t>Sale Of PPE</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n">
+        <v>4000000</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Operating Cash Flow</t>
+          <t>Purchase Of PPE</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>27537000000</v>
+        <v>-623000000</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>19962000000</v>
+        <v>-548000000</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>18085000000</v>
+        <v>-452000000</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>16736000000</v>
+        <v>-424000000</v>
       </c>
       <c r="F38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cash Flow From Continuing Operating Activities</t>
+          <t>Operating Cash Flow</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
@@ -5286,67 +7614,67 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Change In Working Capital</t>
+          <t>Cash Flow From Continuing Operating Activities</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>-8500000000</v>
+        <v>27537000000</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>-4637000000</v>
+        <v>19962000000</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>-1643000000</v>
+        <v>18085000000</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>-1654000000</v>
+        <v>16736000000</v>
       </c>
       <c r="F40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Change In Other Working Capital</t>
+          <t>Change In Working Capital</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>-5155000000</v>
+        <v>-8500000000</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>-7235000000</v>
+        <v>-4637000000</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>-1692000000</v>
+        <v>-1643000000</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>-78000000</v>
+        <v>-1654000000</v>
       </c>
       <c r="F41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Change In Payables And Accrued Expense</t>
+          <t>Change In Other Working Capital</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>-118000000</v>
+        <v>-5155000000</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>121000000</v>
+        <v>-7235000000</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>209000000</v>
+        <v>-1692000000</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>-79000000</v>
+        <v>-78000000</v>
       </c>
       <c r="F42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Change In Payable</t>
+          <t>Change In Payables And Accrued Expense</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
@@ -5366,7 +7694,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Change In Account Payable</t>
+          <t>Change In Payable</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
@@ -5386,47 +7714,47 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Change In Inventory</t>
+          <t>Change In Account Payable</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>-510000000</v>
+        <v>-118000000</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>150000000</v>
+        <v>121000000</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>27000000</v>
+        <v>209000000</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>-627000000</v>
+        <v>-79000000</v>
       </c>
       <c r="F45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Change In Receivables</t>
+          <t>Change In Inventory</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>-2717000000</v>
+        <v>-510000000</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>2327000000</v>
+        <v>150000000</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>-187000000</v>
+        <v>27000000</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>-870000000</v>
+        <v>-627000000</v>
       </c>
       <c r="F46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Changes In Account Receivables</t>
+          <t>Change In Receivables</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
@@ -5446,67 +7774,67 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Other Non Cash Items</t>
+          <t>Changes In Account Receivables</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>438000000</v>
+        <v>-2717000000</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>831000000</v>
+        <v>2327000000</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>141000000</v>
+        <v>-187000000</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>312000000</v>
+        <v>-870000000</v>
       </c>
       <c r="F48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Stock Based Compensation</t>
+          <t>Other Non Cash Items</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>7568000000</v>
+        <v>438000000</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>5741000000</v>
+        <v>831000000</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>2171000000</v>
+        <v>141000000</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>1533000000</v>
+        <v>312000000</v>
       </c>
       <c r="F49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Deferred Tax</t>
+          <t>Stock Based Compensation</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>-4008000000</v>
+        <v>7568000000</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>1965000000</v>
+        <v>5741000000</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>-501000000</v>
+        <v>2171000000</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>-34000000</v>
+        <v>1533000000</v>
       </c>
       <c r="F50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Deferred Income Tax</t>
+          <t>Deferred Tax</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
@@ -5526,27 +7854,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Depreciation Amortization Depletion</t>
+          <t>Deferred Income Tax</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>8775000000</v>
+        <v>-4008000000</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>10010000000</v>
+        <v>1965000000</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>3835000000</v>
+        <v>-501000000</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>4984000000</v>
+        <v>-34000000</v>
       </c>
       <c r="F52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Depreciation And Amortization</t>
+          <t>Depreciation Amortization Depletion</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
@@ -5566,27 +7894,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Amortization Cash Flow</t>
+          <t>Depreciation And Amortization</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>8201000000</v>
+        <v>8775000000</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>9417000000</v>
+        <v>10010000000</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>3333000000</v>
+        <v>3835000000</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>4455000000</v>
+        <v>4984000000</v>
       </c>
       <c r="F54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Amortization Of Intangibles</t>
+          <t>Amortization Cash Flow</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
@@ -5606,75 +7934,95 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Amortization Of Intangibles</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>574000000</v>
+        <v>8201000000</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>593000000</v>
+        <v>9417000000</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>502000000</v>
+        <v>3333000000</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>529000000</v>
+        <v>4455000000</v>
       </c>
       <c r="F56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Operating Gains Losses</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>138000000</v>
+        <v>574000000</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>157000000</v>
-      </c>
-      <c r="D57" s="3" t="n"/>
+        <v>593000000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>502000000</v>
+      </c>
       <c r="E57" s="3" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>198000000</v>
-      </c>
+        <v>529000000</v>
+      </c>
+      <c r="F57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>Operating Gains Losses</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>138000000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>157000000</v>
+      </c>
+      <c r="D58" s="3" t="n"/>
+      <c r="E58" s="3" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>198000000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B58" s="3" t="n">
+      <c r="B59" s="3" t="n">
         <v>23126000000</v>
       </c>
-      <c r="C58" s="3" t="n">
+      <c r="C59" s="3" t="n">
         <v>5895000000</v>
       </c>
-      <c r="D58" s="3" t="n">
+      <c r="D59" s="3" t="n">
         <v>14082000000</v>
       </c>
-      <c r="E58" s="3" t="n">
+      <c r="E59" s="3" t="n">
         <v>11495000000</v>
       </c>
-      <c r="F58" s="3" t="n"/>
+      <c r="F59" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5684,6 +8032,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5694,30 +8043,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-10-31</t>
         </is>
@@ -5730,21 +8084,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>10262000000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>8010000000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>7466000000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>7024000000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>6411000000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>6013000000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5753,21 +8108,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>-600000000</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>-7850000000</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>-58000000</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>-4216000000</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>-2036000000</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5776,21 +8132,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-1250000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-3650000000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>-3638000000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>-6750000000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>-8090000000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5799,21 +8156,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>4474000000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>4483000000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>3587000000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>630000000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>6966000000</v>
-      </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5822,15 +8180,16 @@
         </is>
       </c>
       <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n">
         <v>103000000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n">
         <v>126000000</v>
       </c>
     </row>
@@ -5841,21 +8200,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>-231000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>-250000000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>-237000000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>-142000000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>-144000000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>-100000000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5864,21 +8224,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>695000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>619000000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>699000000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>602000000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>700000000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>671000000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5887,21 +8248,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>1099000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>782000000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>755000000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>822000000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>608000000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>404000000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5910,21 +8272,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>19628000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>14174000000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>16178000000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>10718000000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>9472000000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>9307000000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5933,21 +8296,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>14174000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>16178000000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>10718000000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>9472000000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>9307000000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>9348000000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5956,21 +8320,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>5454000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-2004000000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>5460000000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>1246000000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>165000000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-41000000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5979,21 +8344,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>-4831000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>-10149000000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>-1876000000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>-6014000000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>-6257000000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>-5980000000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6002,21 +8368,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>-4831000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>-10149000000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>-1876000000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>-6014000000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>-6257000000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>-5980000000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6025,21 +8392,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-2000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-37000000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-27000000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>-7000000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>-4000000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>-46000000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6048,957 +8416,1027 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>-3092000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>-3086000000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>-2797000000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>-2786000000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>-2785000000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>-2774000000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Net Common Stock Issuance</t>
+          <t>Common Stock Dividend Paid</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-7850000000</v>
+        <v>-3092000000</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>103000000</v>
+        <v>-3086000000</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-58000000</v>
+        <v>-2797000000</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-4098000000</v>
+        <v>-2786000000</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-2036000000</v>
+        <v>-2785000000</v>
       </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Common Stock Payments</t>
+          <t>Net Common Stock Issuance</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>-487000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>-7850000000</v>
       </c>
-      <c r="C18" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D18" s="3" t="n">
+        <v>103000000</v>
+      </c>
+      <c r="E18" s="3" t="n">
         <v>-58000000</v>
       </c>
-      <c r="E18" s="3" t="n">
-        <v>-4216000000</v>
-      </c>
       <c r="F18" s="3" t="n">
-        <v>-2036000000</v>
+        <v>-4098000000</v>
       </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Common Stock Issuance</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n"/>
+          <t>Common Stock Payments</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>-600000000</v>
+      </c>
       <c r="C19" s="3" t="n">
-        <v>103000000</v>
+        <v>-7850000000</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n">
-        <v>126000000</v>
-      </c>
+      <c r="E19" s="3" t="n">
+        <v>-58000000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>-4216000000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Net Issuance Payments Of Debt</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>824000000</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>845000000</v>
-      </c>
+          <t>Common Stock Issuance</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="n">
-        <v>-3163000000</v>
+        <v>103000000</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>630000000</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>-1124000000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="n"/>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n">
+        <v>126000000</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Net Short Term Debt Issuance</t>
+          <t>Net Issuance Payments Of Debt</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="3" t="n"/>
+        <v>-1250000000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>824000000</v>
+      </c>
       <c r="D21" s="3" t="n">
-        <v>-3373000000</v>
+        <v>845000000</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-119000000</v>
+        <v>-3163000000</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>3980000000</v>
+        <v>630000000</v>
       </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Short Term Debt Issuance</t>
+          <t>Net Short Term Debt Issuance</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n">
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="n">
         <v>-3373000000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-119000000</v>
       </c>
-      <c r="F22" s="3" t="n">
+      <c r="G22" s="3" t="n">
         <v>3980000000</v>
       </c>
-      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Net Long Term Debt Issuance</t>
+          <t>Short Term Debt Issuance</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>824000000</v>
+        <v>0</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1333000000</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>210000000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="n"/>
       <c r="E23" s="3" t="n">
-        <v>749000000</v>
+        <v>-3373000000</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-5104000000</v>
-      </c>
-      <c r="G23" s="3" t="n"/>
+        <v>-119000000</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>3980000000</v>
+      </c>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Long Term Debt Payments</t>
+          <t>Net Long Term Debt Issuance</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>-3650000000</v>
+        <v>-1250000000</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>-3638000000</v>
+        <v>824000000</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>-6750000000</v>
+        <v>1333000000</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>0</v>
+        <v>210000000</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>-8090000000</v>
+        <v>749000000</v>
       </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Long Term Debt Issuance</t>
+          <t>Long Term Debt Payments</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>4474000000</v>
+        <v>-1250000000</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>4971000000</v>
+        <v>-3650000000</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>6960000000</v>
+        <v>-3638000000</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>749000000</v>
+        <v>-6750000000</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>2986000000</v>
+        <v>0</v>
       </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Investing Cash Flow</t>
+          <t>Long Term Debt Issuance</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-115000000</v>
+        <v>0</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-367000000</v>
+        <v>4474000000</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>94000000</v>
+        <v>4971000000</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-133000000</v>
+        <v>6960000000</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-174000000</v>
+        <v>749000000</v>
       </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cash Flow From Continuing Investing Activities</t>
+          <t>Investing Cash Flow</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>-208000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>-115000000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>-367000000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>94000000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>-133000000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>-174000000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Net Other Investing Changes</t>
+          <t>Cash Flow From Continuing Investing Activities</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>5000000</v>
+        <v>-208000000</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>105000000</v>
+        <v>-115000000</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>-16000000</v>
+        <v>-367000000</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>-10000000</v>
+        <v>94000000</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>13000000</v>
+        <v>-133000000</v>
       </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Net Investment Purchase And Sale</t>
+          <t>Net Other Investing Changes</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>130000000</v>
+        <v>7000000</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-235000000</v>
+        <v>5000000</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-48000000</v>
+        <v>105000000</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>21000000</v>
+        <v>-16000000</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-87000000</v>
+        <v>-10000000</v>
       </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sale Of Investment</t>
+          <t>Net Investment Purchase And Sale</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>244000000</v>
+        <v>16000000</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>101000000</v>
+        <v>130000000</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>51000000</v>
+        <v>-235000000</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>78000000</v>
+        <v>-48000000</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>18000000</v>
+        <v>21000000</v>
       </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Purchase Of Investment</t>
+          <t>Sale Of Investment</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-114000000</v>
+        <v>39000000</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-336000000</v>
+        <v>244000000</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-99000000</v>
+        <v>101000000</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-57000000</v>
+        <v>51000000</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-105000000</v>
+        <v>78000000</v>
       </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Net Business Purchase And Sale</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="n"/>
+          <t>Purchase Of Investment</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>-23000000</v>
+      </c>
       <c r="C32" s="3" t="n">
-        <v>0</v>
+        <v>-114000000</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>300000000</v>
+        <v>-336000000</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>0</v>
+        <v>-99000000</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-57000000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sale Of Business</t>
+          <t>Net Business Purchase And Sale</t>
         </is>
       </c>
       <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n">
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n"/>
+      <c r="E33" s="3" t="n">
+        <v>300000000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G33" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="H33" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Purchase Of Business</t>
+          <t>Sale Of Business</t>
         </is>
       </c>
       <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="C34" s="3" t="n"/>
       <c r="D34" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="3" t="n">
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Net PPE Purchase And Sale</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="n">
-        <v>-250000000</v>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>-237000000</v>
-      </c>
+          <t>Purchase Of Business</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="n">
-        <v>-142000000</v>
+        <v>0</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-144000000</v>
+        <v>0</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>-100000000</v>
-      </c>
-      <c r="G35" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Purchase Of PPE</t>
+          <t>Net PPE Purchase And Sale</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>-231000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>-250000000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>-237000000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>-142000000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>-144000000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>-100000000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Operating Cash Flow</t>
+          <t>Purchase Of PPE</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>8260000000</v>
+        <v>-231000000</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>7703000000</v>
+        <v>-250000000</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>7166000000</v>
+        <v>-237000000</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>6555000000</v>
+        <v>-142000000</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>6113000000</v>
+        <v>-144000000</v>
       </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cash Flow From Continuing Operating Activities</t>
+          <t>Operating Cash Flow</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>10493000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>8260000000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>7703000000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>7166000000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>6555000000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>6113000000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Change In Working Capital</t>
+          <t>Cash Flow From Continuing Operating Activities</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>-3105000000</v>
+        <v>10493000000</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>-2345000000</v>
+        <v>8260000000</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>-1894000000</v>
+        <v>7703000000</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>-1910000000</v>
+        <v>7166000000</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>-2351000000</v>
+        <v>6555000000</v>
       </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Change In Other Working Capital</t>
+          <t>Change In Working Capital</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>-1632000000</v>
+        <v>-2572000000</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>-1722000000</v>
+        <v>-3105000000</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>-930000000</v>
+        <v>-2345000000</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>-598000000</v>
+        <v>-1894000000</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>-1905000000</v>
+        <v>-1910000000</v>
       </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Change In Payables And Accrued Expense</t>
+          <t>Change In Other Working Capital</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>534000000</v>
+        <v>1015000000</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>118000000</v>
+        <v>-1632000000</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>136000000</v>
+        <v>-1722000000</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>-613000000</v>
+        <v>-930000000</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>241000000</v>
+        <v>-598000000</v>
       </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Change In Payable</t>
+          <t>Change In Payables And Accrued Expense</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>149000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>534000000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>118000000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>136000000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>-613000000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>241000000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Change In Account Payable</t>
+          <t>Change In Payable</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>149000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>534000000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>118000000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>136000000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>-613000000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>241000000</v>
-      </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Change In Inventory</t>
+          <t>Change In Account Payable</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>-692000000</v>
+        <v>149000000</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>-90000000</v>
+        <v>534000000</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>-163000000</v>
+        <v>118000000</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>-109000000</v>
+        <v>136000000</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>-148000000</v>
+        <v>-613000000</v>
       </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Change In Receivables</t>
+          <t>Change In Inventory</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>-1315000000</v>
+        <v>-1366000000</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>-651000000</v>
+        <v>-692000000</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>-937000000</v>
+        <v>-90000000</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>-590000000</v>
+        <v>-163000000</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>-539000000</v>
+        <v>-109000000</v>
       </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Changes In Account Receivables</t>
+          <t>Change In Receivables</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>-2370000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>-1315000000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>-651000000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>-937000000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>-590000000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>-539000000</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Other Non Cash Items</t>
+          <t>Changes In Account Receivables</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>87000000</v>
+        <v>-2370000000</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>107000000</v>
+        <v>-1315000000</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>59000000</v>
+        <v>-651000000</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>134000000</v>
+        <v>-937000000</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>138000000</v>
+        <v>-590000000</v>
       </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Stock Based Compensation</t>
+          <t>Other Non Cash Items</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2176000000</v>
+        <v>70000000</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2195000000</v>
+        <v>87000000</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2322000000</v>
+        <v>107000000</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1771000000</v>
+        <v>59000000</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1280000000</v>
+        <v>134000000</v>
       </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Deferred Tax</t>
+          <t>Stock Based Compensation</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>-455000000</v>
+        <v>2092000000</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>-3025000000</v>
+        <v>2176000000</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>284000000</v>
+        <v>2195000000</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>-571000000</v>
+        <v>2322000000</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>-696000000</v>
+        <v>1771000000</v>
       </c>
       <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Deferred Income Tax</t>
+          <t>Deferred Tax</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>-603000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>-455000000</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>-3025000000</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="E50" s="3" t="n">
         <v>284000000</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="F50" s="3" t="n">
         <v>-571000000</v>
       </c>
-      <c r="F50" s="3" t="n">
-        <v>-696000000</v>
-      </c>
       <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Depreciation Amortization Depletion</t>
+          <t>Deferred Income Tax</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>2153000000</v>
+        <v>-603000000</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>2233000000</v>
+        <v>-455000000</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>2202000000</v>
+        <v>-3025000000</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>2166000000</v>
+        <v>284000000</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>2174000000</v>
+        <v>-571000000</v>
       </c>
       <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Depreciation And Amortization</t>
+          <t>Depreciation Amortization Depletion</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
+        <v>2165000000</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>2153000000</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="D52" s="3" t="n">
         <v>2233000000</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="E52" s="3" t="n">
         <v>2202000000</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="F52" s="3" t="n">
         <v>2166000000</v>
       </c>
-      <c r="F52" s="3" t="n">
-        <v>2174000000</v>
-      </c>
       <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Amortization Cash Flow</t>
+          <t>Depreciation And Amortization</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>2003000000</v>
+        <v>2165000000</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>2085000000</v>
+        <v>2153000000</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>2060000000</v>
+        <v>2233000000</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>2024000000</v>
+        <v>2202000000</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>2032000000</v>
+        <v>2166000000</v>
       </c>
       <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Amortization Of Intangibles</t>
+          <t>Amortization Cash Flow</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
+        <v>2002000000</v>
+      </c>
+      <c r="C54" s="3" t="n">
         <v>2003000000</v>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="D54" s="3" t="n">
         <v>2085000000</v>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="E54" s="3" t="n">
         <v>2060000000</v>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="F54" s="3" t="n">
         <v>2024000000</v>
       </c>
-      <c r="F54" s="3" t="n">
-        <v>2032000000</v>
-      </c>
       <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Amortization Of Intangibles</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>150000000</v>
+        <v>2002000000</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>148000000</v>
+        <v>2003000000</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>142000000</v>
+        <v>2085000000</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>142000000</v>
+        <v>2060000000</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>142000000</v>
+        <v>2024000000</v>
       </c>
       <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Operating Gains Losses</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>55000000</v>
+        <v>163000000</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>20000000</v>
+        <v>150000000</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>53000000</v>
+        <v>148000000</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>142000000</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>65000000</v>
+        <v>142000000</v>
       </c>
       <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>Operating Gains Losses</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>31000000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>53000000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B57" s="3" t="n">
+      <c r="B58" s="3" t="n">
+        <v>9310000000</v>
+      </c>
+      <c r="C58" s="3" t="n">
         <v>7349000000</v>
       </c>
-      <c r="C57" s="3" t="n">
+      <c r="D58" s="3" t="n">
         <v>8518000000</v>
       </c>
-      <c r="D57" s="3" t="n">
+      <c r="E58" s="3" t="n">
         <v>4140000000</v>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="F58" s="3" t="n">
         <v>4965000000</v>
       </c>
-      <c r="F57" s="3" t="n">
-        <v>5503000000</v>
-      </c>
-      <c r="G57" s="3" t="n"/>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7026,12 +9464,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Gross margin</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>no gaps detected</t>
+          <t>GAAP (statement) ~68% vs yfinance info.grossMargins 76% — info is a non-GAAP basis; FY Summary uses GAAP</t>
         </is>
       </c>
     </row>
